--- a/output/xlsx/all_usecases--GT-.xlsx
+++ b/output/xlsx/all_usecases--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3129" uniqueCount="179">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -32,7 +32,7 @@
     <t>Reduced (Greedy Heuristic - Transition Coverage)</t>
   </si>
   <si>
-    <t>Size: 56 test case(s)</t>
+    <t>Size: 120 test case(s)</t>
   </si>
   <si>
     <t xml:space="preserve">Creation Date: </t>
@@ -489,6 +489,66 @@
   </si>
   <si>
     <t>SYSTEM prompts that If the patient has no current or past prescriptions, the system displays a error message.</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>UC13 View Access Logs</t>
+  </si>
+  <si>
+    <t>A user is a registered user of the iTrust2 Medical Records system (UC1). The user has authenticated himself or herself in the iTrust2 Medical Records system (UC2).</t>
+  </si>
+  <si>
+    <t>user: When the user logs in, their landing screen displays the ten most recent events.</t>
+  </si>
+  <si>
+    <t>SYSTEM When the user logs in, their landing screen displays the ten most recent events.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 1: By default, upon browsing to</t>
+  </si>
+  <si>
+    <t>user: By default, upon browsing to the new page, the user is presented with a list of all entries sorted by dates, most recent access first.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 2: May enter a date range</t>
+  </si>
+  <si>
+    <t>user: The user may enter a date range to view all entries within the range.</t>
+  </si>
+  <si>
+    <t>Exception Flow 1: Enters an invalid date, or enters</t>
+  </si>
+  <si>
+    <t>SYSTEM alerts that The user enters an invalid date, or enters an end date that is before the start date. No events are shown and the user has the opportunity to select different dates.</t>
+  </si>
+  <si>
+    <t>UC14 Alert Users by Email</t>
+  </si>
+  <si>
+    <t>There is an active authenticated session.</t>
+  </si>
+  <si>
+    <t>user: The user has successfully changed his/her password (UC11, S1/S2). An email informing the user of the password change is sent to the user including the MID but not the password.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 1: The status of an appointment</t>
+  </si>
+  <si>
+    <t>hcp: The status of an appointment request has been changed by the HCP involved in the request (UC6, S3). An email informing the patient of their appointment status is sent.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 2: Account has been locked out</t>
+  </si>
+  <si>
+    <t>user: A user account has been locked out, either temporarily or permanently, due to too many failed logins. An email informing the user of their lockout is sent.</t>
+  </si>
+  <si>
+    <t>Exception Flow 1: No valid email associated with account</t>
+  </si>
+  <si>
+    <t>SYSTEM prompts that If the user does not have an email address on file, no email is sent and the failure is logged.</t>
   </si>
 </sst>
 </file>
@@ -580,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F507"/>
+  <dimension ref="A1:F1083"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
@@ -5944,6 +6004,6086 @@
         <v>44</v>
       </c>
     </row>
+    <row r="510">
+      <c r="A510" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B510" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C510" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D510" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B511" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C511" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E511" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B512" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E512" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B513" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B514" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C514" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D514" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E514" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F514" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B515" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="C515" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D515" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="E515" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F515" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B516" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B519" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C519" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D519" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B520" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C520" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E520" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B521" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E521" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B522" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B523" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C523" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D523" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E523" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F523" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B524" t="s" s="3">
+        <v>34</v>
+      </c>
+      <c r="C524" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D524" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="E524" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F524" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B525" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B528" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C528" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D528" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B529" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C529" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E529" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B530" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="E530" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B531" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B532" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C532" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D532" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E532" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F532" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B533" t="s" s="3">
+        <v>37</v>
+      </c>
+      <c r="C533" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D533" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="E533" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F533" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B534" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B537" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C537" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D537" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B538" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C538" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E538" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B539" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E539" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B540" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B541" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C541" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D541" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E541" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F541" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B542" t="s" s="3">
+        <v>40</v>
+      </c>
+      <c r="C542" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D542" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="E542" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F542" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B543" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B546" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C546" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D546" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B547" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C547" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E547" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B548" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="E548" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B549" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B550" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C550" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D550" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E550" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F550" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B551" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="C551" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D551" t="s" s="3">
+        <v>43</v>
+      </c>
+      <c r="E551" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F551" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B552" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B555" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C555" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D555" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B556" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C556" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E556" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B557" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E557" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B558" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B559" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C559" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D559" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E559" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F559" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B560" t="s" s="3">
+        <v>47</v>
+      </c>
+      <c r="C560" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D560" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E560" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F560" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B561" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B564" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C564" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D564" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B565" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C565" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E565" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B566" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="E566" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B567" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B568" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C568" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D568" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E568" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F568" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B569" t="s" s="3">
+        <v>51</v>
+      </c>
+      <c r="C569" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D569" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E569" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F569" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B570" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B573" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C573" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D573" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B574" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C574" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E574" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B575" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="E575" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B576" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B577" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C577" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D577" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E577" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F577" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B578" t="s" s="3">
+        <v>47</v>
+      </c>
+      <c r="C578" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D578" t="s" s="3">
+        <v>53</v>
+      </c>
+      <c r="E578" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F578" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B579" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B582" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C582" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D582" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B583" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C583" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E583" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B584" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="E584" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B585" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B586" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C586" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D586" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E586" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F586" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B587" t="s" s="3">
+        <v>47</v>
+      </c>
+      <c r="C587" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D587" t="s" s="3">
+        <v>55</v>
+      </c>
+      <c r="E587" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F587" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B588" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B591" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C591" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D591" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B592" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C592" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E592" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B593" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E593" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B594" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B595" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C595" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D595" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E595" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F595" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B596" t="s" s="3">
+        <v>47</v>
+      </c>
+      <c r="C596" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D596" t="s" s="3">
+        <v>57</v>
+      </c>
+      <c r="E596" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F596" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B597" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B600" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C600" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D600" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B601" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="C601" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E601" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B602" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="E602" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B603" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B604" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C604" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D604" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E604" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F604" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B605" t="s" s="3">
+        <v>47</v>
+      </c>
+      <c r="C605" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D605" t="s" s="3">
+        <v>60</v>
+      </c>
+      <c r="E605" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F605" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B606" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B609" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C609" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D609" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B610" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C610" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E610" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B611" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="E611" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B612" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B613" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C613" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D613" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E613" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F613" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B614" t="s" s="3">
+        <v>47</v>
+      </c>
+      <c r="C614" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D614" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="E614" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F614" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B615" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B618" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="C618" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D618" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B619" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C619" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E619" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B620" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E620" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B621" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B622" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C622" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D622" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E622" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F622" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B623" t="s" s="3">
+        <v>66</v>
+      </c>
+      <c r="C623" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D623" t="s" s="3">
+        <v>67</v>
+      </c>
+      <c r="E623" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F623" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B624" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B627" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="C627" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D627" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B628" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C628" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E628" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B629" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="E629" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B630" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B631" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C631" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D631" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E631" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F631" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B632" t="s" s="3">
+        <v>66</v>
+      </c>
+      <c r="C632" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D632" t="s" s="3">
+        <v>69</v>
+      </c>
+      <c r="E632" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F632" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B633" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B636" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="C636" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D636" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B637" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C637" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E637" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B638" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="E638" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B639" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B640" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C640" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D640" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E640" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F640" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B641" t="s" s="3">
+        <v>66</v>
+      </c>
+      <c r="C641" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D641" t="s" s="3">
+        <v>71</v>
+      </c>
+      <c r="E641" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F641" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B642" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B645" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="C645" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D645" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B646" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C646" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E646" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B647" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E647" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B648" t="s" s="0">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B649" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C649" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D649" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E649" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F649" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B650" t="s" s="3">
+        <v>162</v>
+      </c>
+      <c r="C650" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D650" t="s" s="3">
+        <v>163</v>
+      </c>
+      <c r="E650" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F650" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B651" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B654" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="C654" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D654" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B655" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C655" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E655" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B656" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="E656" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B657" t="s" s="0">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B658" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C658" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D658" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E658" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F658" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B659" t="s" s="3">
+        <v>165</v>
+      </c>
+      <c r="C659" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D659" t="s" s="3">
+        <v>163</v>
+      </c>
+      <c r="E659" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F659" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B660" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B663" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="C663" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D663" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B664" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C664" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E664" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B665" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="E665" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B666" t="s" s="0">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B667" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C667" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D667" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E667" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F667" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B668" t="s" s="3">
+        <v>167</v>
+      </c>
+      <c r="C668" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D668" t="s" s="3">
+        <v>163</v>
+      </c>
+      <c r="E668" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F668" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B669" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B672" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="C672" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D672" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B673" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C673" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E673" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B674" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="E674" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B675" t="s" s="0">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B676" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C676" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D676" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E676" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F676" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B677" t="s" s="3">
+        <v>162</v>
+      </c>
+      <c r="C677" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D677" t="s" s="3">
+        <v>169</v>
+      </c>
+      <c r="E677" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F677" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B678" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B681" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="C681" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D681" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B682" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C682" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E682" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B683" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E683" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B684" t="s" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B685" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C685" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D685" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E685" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F685" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B686" t="s" s="3">
+        <v>172</v>
+      </c>
+      <c r="C686" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D686" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E686" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F686" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B687" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B690" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="C690" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D690" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B691" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C691" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E691" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B692" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="E692" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B693" t="s" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B694" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C694" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D694" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E694" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F694" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B695" t="s" s="3">
+        <v>174</v>
+      </c>
+      <c r="C695" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D695" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E695" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F695" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B696" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B699" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="C699" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D699" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B700" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C700" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E700" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B701" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="E701" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B702" t="s" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B703" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C703" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D703" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E703" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F703" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B704" t="s" s="3">
+        <v>176</v>
+      </c>
+      <c r="C704" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D704" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E704" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F704" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B705" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B708" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="C708" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D708" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B709" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C709" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E709" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B710" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="E710" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B711" t="s" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B712" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C712" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D712" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E712" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F712" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B713" t="s" s="3">
+        <v>172</v>
+      </c>
+      <c r="C713" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D713" t="s" s="3">
+        <v>178</v>
+      </c>
+      <c r="E713" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F713" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B714" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B717" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="C717" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D717" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B718" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C718" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E718" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B719" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E719" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B720" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B721" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C721" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D721" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E721" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F721" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B722" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="C722" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D722" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E722" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F722" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B723" t="s" s="0">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B726" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="C726" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D726" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B727" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C727" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E727" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B728" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="E728" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B729" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B730" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C730" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D730" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E730" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F730" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B731" t="s" s="3">
+        <v>77</v>
+      </c>
+      <c r="C731" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D731" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E731" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F731" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B732" t="s" s="0">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B735" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="C735" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D735" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B736" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C736" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E736" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B737" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="E737" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B738" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B739" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C739" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D739" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E739" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F739" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B740" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="C740" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D740" t="s" s="3">
+        <v>78</v>
+      </c>
+      <c r="E740" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F740" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B741" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B744" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="C744" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D744" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B745" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C745" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E745" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B746" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="E746" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B747" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B748" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C748" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D748" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E748" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F748" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B749" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="C749" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D749" t="s" s="3">
+        <v>79</v>
+      </c>
+      <c r="E749" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F749" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B750" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B753" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="C753" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D753" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B754" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C754" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E754" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B755" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E755" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B756" t="s" s="0">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B757" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C757" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D757" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E757" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F757" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B758" t="s" s="3">
+        <v>82</v>
+      </c>
+      <c r="C758" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D758" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E758" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F758" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B759" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B762" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="C762" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D762" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B763" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C763" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E763" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B764" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="E764" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B765" t="s" s="0">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B766" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C766" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D766" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E766" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F766" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B767" t="s" s="3">
+        <v>82</v>
+      </c>
+      <c r="C767" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D767" t="s" s="3">
+        <v>84</v>
+      </c>
+      <c r="E767" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F767" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B768" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B771" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="C771" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D771" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B772" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C772" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E772" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B773" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="E773" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B774" t="s" s="0">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B775" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C775" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D775" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E775" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F775" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B776" t="s" s="3">
+        <v>82</v>
+      </c>
+      <c r="C776" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D776" t="s" s="3">
+        <v>86</v>
+      </c>
+      <c r="E776" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F776" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B777" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B780" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="C780" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D780" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B781" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C781" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E781" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B782" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E782" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B783" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B784" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C784" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D784" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E784" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F784" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B785" t="s" s="3">
+        <v>89</v>
+      </c>
+      <c r="C785" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D785" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E785" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F785" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B786" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B789" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="C789" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D789" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B790" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C790" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E790" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B791" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="E791" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B792" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B793" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C793" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D793" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E793" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F793" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B794" t="s" s="3">
+        <v>91</v>
+      </c>
+      <c r="C794" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D794" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E794" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F794" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B795" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B798" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C798" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D798" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B799" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C799" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E799" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B800" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E800" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B801" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B802" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C802" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D802" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E802" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F802" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B803" t="s" s="3">
+        <v>94</v>
+      </c>
+      <c r="C803" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D803" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E803" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F803" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B804" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B807" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C807" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D807" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B808" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C808" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E808" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B809" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="E809" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B810" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B811" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C811" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D811" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E811" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F811" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B812" t="s" s="3">
+        <v>96</v>
+      </c>
+      <c r="C812" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D812" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E812" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F812" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B813" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B816" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C816" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D816" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B817" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C817" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E817" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B818" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="E818" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B819" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B820" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C820" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D820" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E820" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F820" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B821" t="s" s="3">
+        <v>98</v>
+      </c>
+      <c r="C821" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D821" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E821" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F821" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B822" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B825" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C825" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D825" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B826" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C826" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E826" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B827" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="E827" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B828" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B829" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C829" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D829" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E829" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F829" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B830" t="s" s="3">
+        <v>94</v>
+      </c>
+      <c r="C830" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D830" t="s" s="3">
+        <v>99</v>
+      </c>
+      <c r="E830" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F830" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B831" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B834" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C834" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D834" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B835" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C835" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E835" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B836" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E836" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B837" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B838" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C838" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D838" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E838" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F838" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B839" t="s" s="3">
+        <v>102</v>
+      </c>
+      <c r="C839" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D839" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E839" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F839" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B840" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B843" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C843" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D843" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B844" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C844" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E844" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B845" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="E845" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B846" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B847" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C847" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D847" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E847" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F847" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B848" t="s" s="3">
+        <v>104</v>
+      </c>
+      <c r="C848" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D848" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E848" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F848" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B849" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B852" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C852" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D852" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B853" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C853" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E853" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B854" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="E854" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B855" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B856" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C856" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D856" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E856" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F856" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B857" t="s" s="3">
+        <v>102</v>
+      </c>
+      <c r="C857" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D857" t="s" s="3">
+        <v>105</v>
+      </c>
+      <c r="E857" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F857" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B858" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B861" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="C861" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D861" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B862" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C862" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E862" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B863" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E863" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B864" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B865" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C865" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D865" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E865" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F865" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B866" t="s" s="3">
+        <v>108</v>
+      </c>
+      <c r="C866" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D866" t="s" s="3">
+        <v>109</v>
+      </c>
+      <c r="E866" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F866" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B867" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B870" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="C870" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D870" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B871" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C871" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E871" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B872" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="E872" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B873" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B874" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C874" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D874" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E874" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F874" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B875" t="s" s="3">
+        <v>111</v>
+      </c>
+      <c r="C875" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D875" t="s" s="3">
+        <v>109</v>
+      </c>
+      <c r="E875" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F875" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B876" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B879" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="C879" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D879" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B880" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C880" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E880" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B881" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="E881" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B882" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B883" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C883" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D883" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E883" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F883" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B884" t="s" s="3">
+        <v>113</v>
+      </c>
+      <c r="C884" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D884" t="s" s="3">
+        <v>109</v>
+      </c>
+      <c r="E884" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F884" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B885" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B888" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="C888" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D888" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B889" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C889" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E889" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B890" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="E890" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B891" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B892" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C892" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D892" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E892" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F892" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B893" t="s" s="3">
+        <v>115</v>
+      </c>
+      <c r="C893" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D893" t="s" s="3">
+        <v>109</v>
+      </c>
+      <c r="E893" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F893" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B894" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B897" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="C897" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D897" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B898" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C898" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E898" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B899" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="E899" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B900" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B901" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C901" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D901" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E901" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F901" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B902" t="s" s="3">
+        <v>108</v>
+      </c>
+      <c r="C902" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D902" t="s" s="3">
+        <v>116</v>
+      </c>
+      <c r="E902" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F902" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B903" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B906" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="C906" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D906" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B907" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C907" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E907" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B908" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E908" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B909" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B910" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C910" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D910" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E910" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F910" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B911" t="s" s="3">
+        <v>118</v>
+      </c>
+      <c r="C911" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D911" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E911" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F911" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B912" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B915" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="C915" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D915" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B916" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C916" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E916" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B917" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="E917" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B918" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B919" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C919" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D919" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E919" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F919" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B920" t="s" s="3">
+        <v>120</v>
+      </c>
+      <c r="C920" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D920" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E920" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F920" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B921" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B924" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="C924" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D924" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B925" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C925" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E925" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B926" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="E926" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B927" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B928" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C928" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D928" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E928" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F928" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B929" t="s" s="3">
+        <v>122</v>
+      </c>
+      <c r="C929" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D929" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E929" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F929" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B930" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B933" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="C933" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D933" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B934" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C934" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E934" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B935" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="E935" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B936" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B937" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C937" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D937" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E937" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F937" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B938" t="s" s="3">
+        <v>118</v>
+      </c>
+      <c r="C938" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D938" t="s" s="3">
+        <v>123</v>
+      </c>
+      <c r="E938" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F938" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B939" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B942" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="C942" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D942" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B943" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C943" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E943" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B944" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E944" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B945" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B946" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C946" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D946" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E946" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F946" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B947" t="s" s="3">
+        <v>126</v>
+      </c>
+      <c r="C947" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D947" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E947" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F947" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B948" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B951" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="C951" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D951" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B952" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C952" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E952" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B953" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="E953" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B954" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B955" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C955" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D955" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E955" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F955" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B956" t="s" s="3">
+        <v>128</v>
+      </c>
+      <c r="C956" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D956" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E956" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F956" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B957" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B960" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="C960" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D960" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B961" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C961" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E961" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B962" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="E962" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B963" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B964" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C964" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D964" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E964" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F964" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B965" t="s" s="3">
+        <v>130</v>
+      </c>
+      <c r="C965" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D965" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E965" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F965" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B966" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B969" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="C969" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D969" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B970" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C970" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E970" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B971" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="E971" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B972" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B973" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C973" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D973" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E973" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F973" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B974" t="s" s="3">
+        <v>132</v>
+      </c>
+      <c r="C974" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D974" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E974" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F974" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B975" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B978" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="C978" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D978" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B979" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C979" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E979" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B980" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="E980" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B981" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B982" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C982" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D982" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E982" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F982" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B983" t="s" s="3">
+        <v>134</v>
+      </c>
+      <c r="C983" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D983" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E983" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F983" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B984" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B987" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="C987" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D987" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B988" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="C988" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E988" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B989" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="E989" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B990" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B991" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C991" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D991" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E991" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F991" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B992" t="s" s="3">
+        <v>126</v>
+      </c>
+      <c r="C992" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D992" t="s" s="3">
+        <v>135</v>
+      </c>
+      <c r="E992" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F992" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B993" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B996" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="C996" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D996" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B997" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C997" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E997" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B998" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E998" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B999" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1000" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1000" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1000" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1000" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1000" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1001" t="s" s="3">
+        <v>138</v>
+      </c>
+      <c r="C1001" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1001" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1001" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1001" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1002" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1005" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="C1005" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1005" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1006" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C1006" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1006" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1007" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="E1007" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1008" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1009" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1009" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1009" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1009" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1009" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1010" t="s" s="3">
+        <v>140</v>
+      </c>
+      <c r="C1010" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1010" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1010" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1010" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1011" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1014" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="C1014" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1014" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1015" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C1015" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1015" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1016" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="E1016" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1017" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1018" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1018" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1018" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1018" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1018" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1019" t="s" s="3">
+        <v>142</v>
+      </c>
+      <c r="C1019" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1019" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1019" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1019" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1020" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1023" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="C1023" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1023" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1024" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1024" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1024" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1025" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="E1025" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1026" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1027" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1027" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1027" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1027" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1027" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1028" t="s" s="3">
+        <v>144</v>
+      </c>
+      <c r="C1028" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1028" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1028" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1028" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1029" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1032" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="C1032" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1032" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1033" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C1033" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1033" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1034" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="E1034" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1035" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1036" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1036" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1036" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1036" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1036" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1037" t="s" s="3">
+        <v>146</v>
+      </c>
+      <c r="C1037" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1037" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1037" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1037" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1038" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1041" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="C1041" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1041" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1042" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="C1042" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1042" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1043" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="E1043" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1044" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1045" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1045" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1045" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1045" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1045" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1046" t="s" s="3">
+        <v>148</v>
+      </c>
+      <c r="C1046" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1046" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1046" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1046" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1047" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1050" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="C1050" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1050" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1051" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C1051" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1051" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1052" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="E1052" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1053" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1054" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1054" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1054" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1054" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1054" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1055" t="s" s="3">
+        <v>150</v>
+      </c>
+      <c r="C1055" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1055" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1055" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1055" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1056" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1059" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="C1059" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1059" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1060" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="C1060" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1060" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1061" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="E1061" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1062" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1063" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1063" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1063" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1063" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1063" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1064" t="s" s="3">
+        <v>153</v>
+      </c>
+      <c r="C1064" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1064" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1064" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1064" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1065" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1068" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="C1068" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1068" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1069" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="C1069" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1069" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1070" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="E1070" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1071" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1072" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1072" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1072" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1072" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1072" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1073" t="s" s="3">
+        <v>138</v>
+      </c>
+      <c r="C1073" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1073" t="s" s="3">
+        <v>155</v>
+      </c>
+      <c r="E1073" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1073" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1074" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1077" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="C1077" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1077" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1078" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="C1078" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1078" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1079" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="E1079" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1080" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1081" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1081" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1081" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1081" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1081" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1082" t="s" s="3">
+        <v>138</v>
+      </c>
+      <c r="C1082" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1082" t="s" s="3">
+        <v>158</v>
+      </c>
+      <c r="E1082" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1082" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1083" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/output/xlsx/all_usecases--GT-.xlsx
+++ b/output/xlsx/all_usecases--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3129" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4065" uniqueCount="240">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -32,7 +32,7 @@
     <t>Reduced (Greedy Heuristic - Transition Coverage)</t>
   </si>
   <si>
-    <t>Size: 120 test case(s)</t>
+    <t>Size: 156 test case(s)</t>
   </si>
   <si>
     <t xml:space="preserve">Creation Date: </t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Version: </t>
   </si>
   <si>
-    <t>1.0</t>
+    <t>2.0</t>
   </si>
   <si>
     <t xml:space="preserve">Test Case ID: </t>
@@ -230,6 +230,63 @@
     <t>SYSTEM prompts that A warning is shown about unsaved changes that will be lost. If they repeat the action, the new patient's data is loaded .</t>
   </si>
   <si>
+    <t>UC13 View Access Logs</t>
+  </si>
+  <si>
+    <t>A user is a registered user of the iTrust2 Medical Records system (UC1). The user has authenticated himself or herself in the iTrust2 Medical Records system (UC2).</t>
+  </si>
+  <si>
+    <t>user: When the user logs in, their landing screen displays the ten most recent events.</t>
+  </si>
+  <si>
+    <t>SYSTEM When the user logs in, their landing screen displays the ten most recent events.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 1: By default, upon browsing to</t>
+  </si>
+  <si>
+    <t>user: By default, upon browsing to the new page, the user is presented with a list of all entries sorted by dates, most recent access first.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 2: May enter a date range</t>
+  </si>
+  <si>
+    <t>user: The user may enter a date range to view all entries within the range.</t>
+  </si>
+  <si>
+    <t>Exception Flow 1: Enters an invalid date, or enters</t>
+  </si>
+  <si>
+    <t>SYSTEM alerts that The user enters an invalid date, or enters an end date that is before the start date. No events are shown and the user has the opportunity to select different dates.</t>
+  </si>
+  <si>
+    <t>UC14 Alert Users by Email</t>
+  </si>
+  <si>
+    <t>There is an active authenticated session.</t>
+  </si>
+  <si>
+    <t>user: The user has successfully changed his/her password (UC11, S1/S2). An email informing the user of the password change is sent to the user including the MID but not the password.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 1: The status of an appointment</t>
+  </si>
+  <si>
+    <t>hcp: The status of an appointment request has been changed by the HCP involved in the request (UC6, S3). An email informing the patient of their appointment status is sent.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 2: Account has been locked out</t>
+  </si>
+  <si>
+    <t>user: A user account has been locked out, either temporarily or permanently, due to too many failed logins. An email informing the user of their lockout is sent.</t>
+  </si>
+  <si>
+    <t>Exception Flow 1: No valid email associated with account</t>
+  </si>
+  <si>
+    <t>SYSTEM prompts that If the user does not have an email address on file, no email is sent and the failure is logged.</t>
+  </si>
+  <si>
     <t>UC1 User Functionality</t>
   </si>
   <si>
@@ -491,64 +548,190 @@
     <t>SYSTEM prompts that If the patient has no current or past prescriptions, the system displays a error message.</t>
   </si>
   <si>
-    <t>2.0</t>
-  </si>
-  <si>
-    <t>UC13 View Access Logs</t>
-  </si>
-  <si>
-    <t>A user is a registered user of the iTrust2 Medical Records system (UC1). The user has authenticated himself or herself in the iTrust2 Medical Records system (UC2).</t>
-  </si>
-  <si>
-    <t>user: When the user logs in, their landing screen displays the ten most recent events.</t>
-  </si>
-  <si>
-    <t>SYSTEM When the user logs in, their landing screen displays the ten most recent events.</t>
-  </si>
-  <si>
-    <t>Alternative Flow 1: By default, upon browsing to</t>
-  </si>
-  <si>
-    <t>user: By default, upon browsing to the new page, the user is presented with a list of all entries sorted by dates, most recent access first.</t>
-  </si>
-  <si>
-    <t>Alternative Flow 2: May enter a date range</t>
-  </si>
-  <si>
-    <t>user: The user may enter a date range to view all entries within the range.</t>
-  </si>
-  <si>
-    <t>Exception Flow 1: Enters an invalid date, or enters</t>
-  </si>
-  <si>
-    <t>SYSTEM alerts that The user enters an invalid date, or enters an end date that is before the start date. No events are shown and the user has the opportunity to select different dates.</t>
-  </si>
-  <si>
-    <t>UC14 Alert Users by Email</t>
-  </si>
-  <si>
-    <t>There is an active authenticated session.</t>
-  </si>
-  <si>
-    <t>user: The user has successfully changed his/her password (UC11, S1/S2). An email informing the user of the password change is sent to the user including the MID but not the password.</t>
-  </si>
-  <si>
-    <t>Alternative Flow 1: The status of an appointment</t>
-  </si>
-  <si>
-    <t>hcp: The status of an appointment request has been changed by the HCP involved in the request (UC6, S3). An email informing the patient of their appointment status is sent.</t>
-  </si>
-  <si>
-    <t>Alternative Flow 2: Account has been locked out</t>
-  </si>
-  <si>
-    <t>user: A user account has been locked out, either temporarily or permanently, due to too many failed logins. An email informing the user of their lockout is sent.</t>
-  </si>
-  <si>
-    <t>Exception Flow 1: No valid email associated with account</t>
-  </si>
-  <si>
-    <t>SYSTEM prompts that If the user does not have an email address on file, no email is sent and the failure is logged.</t>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>UC15 Emergency Health Records</t>
+  </si>
+  <si>
+    <t>An HCP is a registered user of the iTrust2 system (UC1). The HCP has authenticated in the system (UC2). An Emergency Responder is a registered user of the iTrust2 system (UC1). The Emergency Responder has authenticated in the system (UC2).</t>
+  </si>
+  <si>
+    <t>user: The approved user enters the desired patients First and/or Last Name (or a correct substring of either/both) into the search box. The patients with first/last names containing the substring(s) provided are shown.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 1: The approved user enters the</t>
+  </si>
+  <si>
+    <t>user: The approved user enters the desired patients MID (username), or a correct substring of it, in the search box. The patient/s matching the MID/MID substring are displayed.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 2: Record for</t>
+  </si>
+  <si>
+    <t>patient: The approved user selects the patient they wish to see the Emergency Health Records for. The patients Emergency Health Records page is pulled up. The patients name, age, date of birth, gender, and blood type are neatly displayed, followed by a list of all diagnosis codes for short-term diagnoses within the last 60 days (sorted by most recent first). Lastly, a list of all prescriptions the patient has received in the last 90 days is shown (sorted by most recent first).</t>
+  </si>
+  <si>
+    <t>SYSTEM prompts that No users are displayed if the input does not conform to appropriate data formats as specified in 15.6.</t>
+  </si>
+  <si>
+    <t>Exception Flow 2: No users are displayed if a</t>
+  </si>
+  <si>
+    <t>SYSTEM prompts that No users are displayed if a user with the provided first and/or last name substring does not exist. (Note the name can be partial, but it must be correct. 'Ale' would match 'Alex' as a first name, but 'Ael' would not.</t>
+  </si>
+  <si>
+    <t>Exception Flow 3: No users are displayed if a</t>
+  </si>
+  <si>
+    <t>SYSTEM prompts that No users are displayed if a user with the provided MID/Username does not exist or if the provided MID substring is not found in any existing MIDs.</t>
+  </si>
+  <si>
+    <t>UC16 Personal Representatives</t>
+  </si>
+  <si>
+    <t>The iTrust2 user has authenticated themselves in iTrust2 (UC2). as a patient Another patient is a registered user of the iTrust2 Medical Records system . The patient has authenticated themselves in the iTrust2 Medical Records system (UC1).. An HCP is a registered user of the iTrust2 Medical Records system (UC1). The HCP has authenticated themselves in the iTrust2 Medical Records system (UC2).</t>
+  </si>
+  <si>
+    <t>user: Patients have the ability to view the list of people they are a PR for and who they have assigned as a PR . The patient can declare and un-declare other users as personal representatives of themselves , as well as un-declare themselves as a personal representative as someone . HCPs can assign one patient as a PR for another and view their assigned PRs and assignees .</t>
+  </si>
+  <si>
+    <t>Exception Flow 1: An error message is shown that</t>
+  </si>
+  <si>
+    <t>SYSTEM prompts that An error message is shown that the user is not found or the action was not completed successfully. User is returned to form to try again</t>
+  </si>
+  <si>
+    <t>UC17 Lab Procedures</t>
+  </si>
+  <si>
+    <t>The iTrust2 Admin has authenticated themselves in the iTrust2 Medical Records system . A Patient is a registered user of the iTrust2 Medical Records system . The Patient has authenticated themselves in the iTrust2 Medical Records system . A Lab Tech is a registered user of the iTrust2 Medical Records system . The Lab Tech has authenticated themselves in the iTrust2 Medical Records system . A Lab Tech is a registered user of the iTrust2 Medical Records system . The Lab Tech has authenticated themselves in the iTrust2 Medical Records system . An HCP is a registered user of the iTrust2 Medical Records system . The HCP has authenticated themselves in the iTrust2 Medical Records system . The HCP has started documenting an office visit, including basic health metrics, for the patient [UC7 &amp; UC8].</t>
+  </si>
+  <si>
+    <t>admin: The administrator enters the LOINC code, Long Common Name, Component, and Property of the procedure. They press Add Procedure .</t>
+  </si>
+  <si>
+    <t>SYSTEM A message shows if the procedure was entered correctly.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 1: Edit procedure</t>
+  </si>
+  <si>
+    <t>admin: The administrator selects a procedure from the list of possible procedure, and presses Edit Procedure to edit the procedure. They can then change the LOINC code, common name, property, and description of the procedure. They press Submit .</t>
+  </si>
+  <si>
+    <t>Alternative Flow 2: Delete it</t>
+  </si>
+  <si>
+    <t>admin: The administrator presses the Delete button associated with a LOINC procedure to delete it.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 3: Add procedure</t>
+  </si>
+  <si>
+    <t>hcp: The HCP selects the correct procedure from the menu of procedure options labeled by their LOINC codes and descriptions. They enter the following additional information about the procedure: the priority from 1 to 4 (1 being highest), the lab tech who will perform the procedure, and any comments. They press the Add Procedure button.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 4: View assigned procedures</t>
+  </si>
+  <si>
+    <t>admin: The lab tech selects to view their assigned procedures and data corresponding to the procedure. They can update the current status of the procedure. They can edit the current comment on the procedure, if they change the status to Completed. They can also select another lab tech, and assign the procedure to them.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 5: View an office</t>
+  </si>
+  <si>
+    <t>patient: The patient or HCP selects to view an office visit. They see all information pertaining to any procedures associated with the office visit, including LOINC code, priority, date, comment, and status. The patient cannot edit the information. The HCP can delete any procedure with a status of Assigned.</t>
+  </si>
+  <si>
+    <t>SYSTEM prompts that An error message is displayed describing what entries do not conform to appropriate data formats as specified in 17.6. The user may make changes to the form and try to submit again.</t>
+  </si>
+  <si>
+    <t>UC18 Vaccinations</t>
+  </si>
+  <si>
+    <t>An HCP, a patient, and an administrator are all registered in the iTrust2 system. An iTrust2 user is logged into the system.</t>
+  </si>
+  <si>
+    <t>admin: The admin is taken to a page where a list of all vaccines are displayed. The admin clicks the Add Vaccine button.</t>
+  </si>
+  <si>
+    <t>SYSTEM The admin is taken to a page where they can enter the information for the vaccine, including: Name of vaccination Abbreviation CPT Code Comments The admin presses the Submit Vaccine button , and a message is displayed.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 1: Is taken to a page</t>
+  </si>
+  <si>
+    <t>admin: The admin is taken to a page where a list of all vaccine are displayed. The admin selects a vaccine to edit and clicks the Edit Vaccine button. The fields of the vaccine are displayed, and the admin can update a field.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 2: Is taken to a page</t>
+  </si>
+  <si>
+    <t>admin: The admin is taken to a page where a list of all vaccine are displayed.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 3: When documenting an office visit</t>
+  </si>
+  <si>
+    <t>hcp: When documenting an office visit, an HCP can select zero or more vaccines from a list of all vaccines to add to the office visit. The vaccination will be added to the office visit in the patient's records.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 4: Or hcp selects an office</t>
+  </si>
+  <si>
+    <t>patient: The patient or HCP selects an office visit to view. They can see all of the vaccinations that pertain to that office visit. The patient cannot edit the information.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 5: Is taken to a page</t>
+  </si>
+  <si>
+    <t>patient: The patient is taken to a page where a list of all of their vaccinations are displayed. They can view all of the information pertaining to each vaccination record. The patient cannot edit the information.</t>
+  </si>
+  <si>
+    <t>Alternative Flow 6: Can look up a patient</t>
+  </si>
+  <si>
+    <t>patient: An HCP can look up a patient by name and view their vaccination record. A list of all of the vaccinations administered to that patient are displayed, and all information pertaining to each vaccination record is displayed.</t>
+  </si>
+  <si>
+    <t>SYSTEM prompts that An error message is displayed if the entered information does not fit the data formats specified in 18.6. Otherwise, a success message is displayed.</t>
+  </si>
+  <si>
+    <t>UC19 Food Diary</t>
+  </si>
+  <si>
+    <t>The iTrust2 user has authenticated themselves in iTrust2 (UC2) as a patient or HCP.</t>
+  </si>
+  <si>
+    <t>patient: Any patient may select to either view their food diary or add a new diary entry. If the patient selects to view their food diary, every diary entry is displayed with the information contained in with the most recent entries (by date of the entry in the food diary) being displayed first and calculates totals with . If patient selects to add a new diary entry, they enter the required information into the form . The patient submits the form and is sent to the page to view their food diary. Any HCP may view food diary entries (but may not create them) for a patient in the iTrust2 system. The HCP may search for patients, and upon selecting one, will see a food diary displayed exactly as the patient would .</t>
+  </si>
+  <si>
+    <t>Exception Flow 1: If there are no food diary</t>
+  </si>
+  <si>
+    <t>SYSTEM prompts that If there are no Food Diary Entries for the patient, a message is displayed that there are none.</t>
+  </si>
+  <si>
+    <t>Exception Flow 2: Invalid inputs are flagged and an</t>
+  </si>
+  <si>
+    <t>SYSTEM prompts that Invalid inputs are flagged and an error message appropriate to the input is printed.</t>
+  </si>
+  <si>
+    <t>admin: An Admin enters a user name, a password, confirm password, the role, and if the user is enabled (or active) in the system. The Admin presses the button to add the user . The user name serves as the User's Medical ID (MID). The possible roles are: Patient Health Care Provider (HCP) Admin Emergency Responder (ER) Lab Tech</t>
+  </si>
+  <si>
+    <t>Alternative Flow 3: An er may enter or</t>
+  </si>
+  <si>
+    <t>patient: An ER may enter or edit their own demographic information according to the data format in Section 4.6 .</t>
+  </si>
+  <si>
+    <t>Alternative Flow 4: A lab tech may enter</t>
+  </si>
+  <si>
+    <t>patient: A Lab Tech may enter or edit their own demographic information according to the data format in Section 4.6 .</t>
   </si>
 </sst>
 </file>
@@ -640,7 +823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F1083"/>
+  <dimension ref="A1:F1407"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
@@ -2187,7 +2370,7 @@
         <v>28</v>
       </c>
       <c r="D146" t="s" s="3">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="E146" t="s" s="3">
         <v>28</v>
@@ -2201,7 +2384,7 @@
         <v>30</v>
       </c>
       <c r="B147" t="s" s="0">
-        <v>75</v>
+        <v>49</v>
       </c>
     </row>
     <row r="150">
@@ -2282,7 +2465,7 @@
         <v>28</v>
       </c>
       <c r="D155" t="s" s="3">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="E155" t="s" s="3">
         <v>28</v>
@@ -2296,7 +2479,7 @@
         <v>30</v>
       </c>
       <c r="B156" t="s" s="0">
-        <v>75</v>
+        <v>49</v>
       </c>
     </row>
     <row r="159">
@@ -2332,7 +2515,7 @@
         <v>16</v>
       </c>
       <c r="B161" t="s" s="0">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="E161" t="s" s="1">
         <v>18</v>
@@ -2371,13 +2554,13 @@
         <v>1.0</v>
       </c>
       <c r="B164" t="s" s="3">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C164" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D164" t="s" s="3">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E164" t="s" s="3">
         <v>28</v>
@@ -2391,7 +2574,7 @@
         <v>30</v>
       </c>
       <c r="B165" t="s" s="0">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="168">
@@ -2427,7 +2610,7 @@
         <v>16</v>
       </c>
       <c r="B170" t="s" s="0">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="E170" t="s" s="1">
         <v>18</v>
@@ -2472,7 +2655,7 @@
         <v>28</v>
       </c>
       <c r="D173" t="s" s="3">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E173" t="s" s="3">
         <v>28</v>
@@ -2494,7 +2677,7 @@
         <v>2</v>
       </c>
       <c r="B177" t="s" s="0">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C177" t="s" s="1">
         <v>10</v>
@@ -2533,7 +2716,7 @@
         <v>19</v>
       </c>
       <c r="B180" t="s" s="0">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="181">
@@ -2561,7 +2744,7 @@
         <v>1.0</v>
       </c>
       <c r="B182" t="s" s="3">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C182" t="s" s="3">
         <v>28</v>
@@ -2589,7 +2772,7 @@
         <v>2</v>
       </c>
       <c r="B186" t="s" s="0">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C186" t="s" s="1">
         <v>10</v>
@@ -2617,7 +2800,7 @@
         <v>16</v>
       </c>
       <c r="B188" t="s" s="0">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E188" t="s" s="1">
         <v>18</v>
@@ -2628,7 +2811,7 @@
         <v>19</v>
       </c>
       <c r="B189" t="s" s="0">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="190">
@@ -2656,13 +2839,13 @@
         <v>1.0</v>
       </c>
       <c r="B191" t="s" s="3">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C191" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D191" t="s" s="3">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="E191" t="s" s="3">
         <v>28</v>
@@ -2676,7 +2859,7 @@
         <v>30</v>
       </c>
       <c r="B192" t="s" s="0">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="195">
@@ -2684,7 +2867,7 @@
         <v>2</v>
       </c>
       <c r="B195" t="s" s="0">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C195" t="s" s="1">
         <v>10</v>
@@ -2712,7 +2895,7 @@
         <v>16</v>
       </c>
       <c r="B197" t="s" s="0">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E197" t="s" s="1">
         <v>18</v>
@@ -2723,7 +2906,7 @@
         <v>19</v>
       </c>
       <c r="B198" t="s" s="0">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="199">
@@ -2751,13 +2934,13 @@
         <v>1.0</v>
       </c>
       <c r="B200" t="s" s="3">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C200" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D200" t="s" s="3">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="E200" t="s" s="3">
         <v>28</v>
@@ -2771,7 +2954,7 @@
         <v>30</v>
       </c>
       <c r="B201" t="s" s="0">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="204">
@@ -2779,7 +2962,7 @@
         <v>2</v>
       </c>
       <c r="B204" t="s" s="0">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C204" t="s" s="1">
         <v>10</v>
@@ -2793,7 +2976,7 @@
         <v>12</v>
       </c>
       <c r="B205" t="s" s="0">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C205" t="s" s="1">
         <v>14</v>
@@ -2807,7 +2990,7 @@
         <v>16</v>
       </c>
       <c r="B206" t="s" s="0">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="E206" t="s" s="1">
         <v>18</v>
@@ -2818,7 +3001,7 @@
         <v>19</v>
       </c>
       <c r="B207" t="s" s="0">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="208">
@@ -2846,13 +3029,13 @@
         <v>1.0</v>
       </c>
       <c r="B209" t="s" s="3">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C209" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D209" t="s" s="3">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="E209" t="s" s="3">
         <v>28</v>
@@ -2866,7 +3049,7 @@
         <v>30</v>
       </c>
       <c r="B210" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="213">
@@ -2874,7 +3057,7 @@
         <v>2</v>
       </c>
       <c r="B213" t="s" s="0">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C213" t="s" s="1">
         <v>10</v>
@@ -2888,7 +3071,7 @@
         <v>12</v>
       </c>
       <c r="B214" t="s" s="0">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C214" t="s" s="1">
         <v>14</v>
@@ -2902,7 +3085,7 @@
         <v>16</v>
       </c>
       <c r="B215" t="s" s="0">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="E215" t="s" s="1">
         <v>18</v>
@@ -2913,7 +3096,7 @@
         <v>19</v>
       </c>
       <c r="B216" t="s" s="0">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="217">
@@ -2941,7 +3124,7 @@
         <v>1.0</v>
       </c>
       <c r="B218" t="s" s="3">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C218" t="s" s="3">
         <v>28</v>
@@ -2961,7 +3144,7 @@
         <v>30</v>
       </c>
       <c r="B219" t="s" s="0">
-        <v>49</v>
+        <v>94</v>
       </c>
     </row>
     <row r="222">
@@ -2969,7 +3152,7 @@
         <v>2</v>
       </c>
       <c r="B222" t="s" s="0">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C222" t="s" s="1">
         <v>10</v>
@@ -2983,7 +3166,7 @@
         <v>12</v>
       </c>
       <c r="B223" t="s" s="0">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C223" t="s" s="1">
         <v>14</v>
@@ -2997,7 +3180,7 @@
         <v>16</v>
       </c>
       <c r="B224" t="s" s="0">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="E224" t="s" s="1">
         <v>18</v>
@@ -3008,7 +3191,7 @@
         <v>19</v>
       </c>
       <c r="B225" t="s" s="0">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="226">
@@ -3036,7 +3219,7 @@
         <v>1.0</v>
       </c>
       <c r="B227" t="s" s="3">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C227" t="s" s="3">
         <v>28</v>
@@ -3056,7 +3239,7 @@
         <v>30</v>
       </c>
       <c r="B228" t="s" s="0">
-        <v>49</v>
+        <v>94</v>
       </c>
     </row>
     <row r="231">
@@ -3064,7 +3247,7 @@
         <v>2</v>
       </c>
       <c r="B231" t="s" s="0">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C231" t="s" s="1">
         <v>10</v>
@@ -3078,7 +3261,7 @@
         <v>12</v>
       </c>
       <c r="B232" t="s" s="0">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C232" t="s" s="1">
         <v>14</v>
@@ -3092,7 +3275,7 @@
         <v>16</v>
       </c>
       <c r="B233" t="s" s="0">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="E233" t="s" s="1">
         <v>18</v>
@@ -3103,7 +3286,7 @@
         <v>19</v>
       </c>
       <c r="B234" t="s" s="0">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="235">
@@ -3131,13 +3314,13 @@
         <v>1.0</v>
       </c>
       <c r="B236" t="s" s="3">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C236" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D236" t="s" s="3">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="E236" t="s" s="3">
         <v>28</v>
@@ -3151,7 +3334,7 @@
         <v>30</v>
       </c>
       <c r="B237" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="240">
@@ -3159,7 +3342,7 @@
         <v>2</v>
       </c>
       <c r="B240" t="s" s="0">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C240" t="s" s="1">
         <v>10</v>
@@ -3173,7 +3356,7 @@
         <v>12</v>
       </c>
       <c r="B241" t="s" s="0">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C241" t="s" s="1">
         <v>14</v>
@@ -3187,7 +3370,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s" s="0">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="E242" t="s" s="1">
         <v>18</v>
@@ -3198,7 +3381,7 @@
         <v>19</v>
       </c>
       <c r="B243" t="s" s="0">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="244">
@@ -3226,13 +3409,13 @@
         <v>1.0</v>
       </c>
       <c r="B245" t="s" s="3">
+        <v>93</v>
+      </c>
+      <c r="C245" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D245" t="s" s="3">
         <v>98</v>
-      </c>
-      <c r="C245" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="D245" t="s" s="3">
-        <v>48</v>
       </c>
       <c r="E245" t="s" s="3">
         <v>28</v>
@@ -3246,7 +3429,7 @@
         <v>30</v>
       </c>
       <c r="B246" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="249">
@@ -3254,7 +3437,7 @@
         <v>2</v>
       </c>
       <c r="B249" t="s" s="0">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C249" t="s" s="1">
         <v>10</v>
@@ -3268,7 +3451,7 @@
         <v>12</v>
       </c>
       <c r="B250" t="s" s="0">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C250" t="s" s="1">
         <v>14</v>
@@ -3282,7 +3465,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s" s="0">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="E251" t="s" s="1">
         <v>18</v>
@@ -3293,7 +3476,7 @@
         <v>19</v>
       </c>
       <c r="B252" t="s" s="0">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="253">
@@ -3321,13 +3504,13 @@
         <v>1.0</v>
       </c>
       <c r="B254" t="s" s="3">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C254" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D254" t="s" s="3">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="E254" t="s" s="3">
         <v>28</v>
@@ -3341,7 +3524,7 @@
         <v>30</v>
       </c>
       <c r="B255" t="s" s="0">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="258">
@@ -3349,7 +3532,7 @@
         <v>2</v>
       </c>
       <c r="B258" t="s" s="0">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C258" t="s" s="1">
         <v>10</v>
@@ -3363,7 +3546,7 @@
         <v>12</v>
       </c>
       <c r="B259" t="s" s="0">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C259" t="s" s="1">
         <v>14</v>
@@ -3377,7 +3560,7 @@
         <v>16</v>
       </c>
       <c r="B260" t="s" s="0">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="E260" t="s" s="1">
         <v>18</v>
@@ -3388,7 +3571,7 @@
         <v>19</v>
       </c>
       <c r="B261" t="s" s="0">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="262">
@@ -3416,13 +3599,13 @@
         <v>1.0</v>
       </c>
       <c r="B263" t="s" s="3">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C263" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D263" t="s" s="3">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="E263" t="s" s="3">
         <v>28</v>
@@ -3436,7 +3619,7 @@
         <v>30</v>
       </c>
       <c r="B264" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="267">
@@ -3444,7 +3627,7 @@
         <v>2</v>
       </c>
       <c r="B267" t="s" s="0">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C267" t="s" s="1">
         <v>10</v>
@@ -3458,7 +3641,7 @@
         <v>12</v>
       </c>
       <c r="B268" t="s" s="0">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C268" t="s" s="1">
         <v>14</v>
@@ -3472,7 +3655,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s" s="0">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E269" t="s" s="1">
         <v>18</v>
@@ -3483,7 +3666,7 @@
         <v>19</v>
       </c>
       <c r="B270" t="s" s="0">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="271">
@@ -3511,13 +3694,13 @@
         <v>1.0</v>
       </c>
       <c r="B272" t="s" s="3">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C272" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D272" t="s" s="3">
-        <v>48</v>
+        <v>105</v>
       </c>
       <c r="E272" t="s" s="3">
         <v>28</v>
@@ -3531,7 +3714,7 @@
         <v>30</v>
       </c>
       <c r="B273" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="276">
@@ -3539,7 +3722,7 @@
         <v>2</v>
       </c>
       <c r="B276" t="s" s="0">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C276" t="s" s="1">
         <v>10</v>
@@ -3553,7 +3736,7 @@
         <v>12</v>
       </c>
       <c r="B277" t="s" s="0">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C277" t="s" s="1">
         <v>14</v>
@@ -3567,7 +3750,7 @@
         <v>16</v>
       </c>
       <c r="B278" t="s" s="0">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="E278" t="s" s="1">
         <v>18</v>
@@ -3578,7 +3761,7 @@
         <v>19</v>
       </c>
       <c r="B279" t="s" s="0">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="280">
@@ -3606,13 +3789,13 @@
         <v>1.0</v>
       </c>
       <c r="B281" t="s" s="3">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C281" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D281" t="s" s="3">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="E281" t="s" s="3">
         <v>28</v>
@@ -3626,7 +3809,7 @@
         <v>30</v>
       </c>
       <c r="B282" t="s" s="0">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="285">
@@ -3648,7 +3831,7 @@
         <v>12</v>
       </c>
       <c r="B286" t="s" s="0">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C286" t="s" s="1">
         <v>14</v>
@@ -3662,7 +3845,7 @@
         <v>16</v>
       </c>
       <c r="B287" t="s" s="0">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="E287" t="s" s="1">
         <v>18</v>
@@ -3701,13 +3884,13 @@
         <v>1.0</v>
       </c>
       <c r="B290" t="s" s="3">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C290" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D290" t="s" s="3">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="E290" t="s" s="3">
         <v>28</v>
@@ -3729,7 +3912,7 @@
         <v>2</v>
       </c>
       <c r="B294" t="s" s="0">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C294" t="s" s="1">
         <v>10</v>
@@ -3743,7 +3926,7 @@
         <v>12</v>
       </c>
       <c r="B295" t="s" s="0">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C295" t="s" s="1">
         <v>14</v>
@@ -3757,7 +3940,7 @@
         <v>16</v>
       </c>
       <c r="B296" t="s" s="0">
-        <v>110</v>
+        <v>17</v>
       </c>
       <c r="E296" t="s" s="1">
         <v>18</v>
@@ -3768,7 +3951,7 @@
         <v>19</v>
       </c>
       <c r="B297" t="s" s="0">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="298">
@@ -3796,13 +3979,13 @@
         <v>1.0</v>
       </c>
       <c r="B299" t="s" s="3">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C299" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D299" t="s" s="3">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="E299" t="s" s="3">
         <v>28</v>
@@ -3824,7 +4007,7 @@
         <v>2</v>
       </c>
       <c r="B303" t="s" s="0">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C303" t="s" s="1">
         <v>10</v>
@@ -3838,7 +4021,7 @@
         <v>12</v>
       </c>
       <c r="B304" t="s" s="0">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C304" t="s" s="1">
         <v>14</v>
@@ -3852,7 +4035,7 @@
         <v>16</v>
       </c>
       <c r="B305" t="s" s="0">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E305" t="s" s="1">
         <v>18</v>
@@ -3863,7 +4046,7 @@
         <v>19</v>
       </c>
       <c r="B306" t="s" s="0">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="307">
@@ -3891,13 +4074,13 @@
         <v>1.0</v>
       </c>
       <c r="B308" t="s" s="3">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C308" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D308" t="s" s="3">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="E308" t="s" s="3">
         <v>28</v>
@@ -3919,7 +4102,7 @@
         <v>2</v>
       </c>
       <c r="B312" t="s" s="0">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C312" t="s" s="1">
         <v>10</v>
@@ -3933,7 +4116,7 @@
         <v>12</v>
       </c>
       <c r="B313" t="s" s="0">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C313" t="s" s="1">
         <v>14</v>
@@ -3947,7 +4130,7 @@
         <v>16</v>
       </c>
       <c r="B314" t="s" s="0">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E314" t="s" s="1">
         <v>18</v>
@@ -3958,7 +4141,7 @@
         <v>19</v>
       </c>
       <c r="B315" t="s" s="0">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="316">
@@ -3986,13 +4169,13 @@
         <v>1.0</v>
       </c>
       <c r="B317" t="s" s="3">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C317" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D317" t="s" s="3">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="E317" t="s" s="3">
         <v>28</v>
@@ -4014,7 +4197,7 @@
         <v>2</v>
       </c>
       <c r="B321" t="s" s="0">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C321" t="s" s="1">
         <v>10</v>
@@ -4028,7 +4211,7 @@
         <v>12</v>
       </c>
       <c r="B322" t="s" s="0">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C322" t="s" s="1">
         <v>14</v>
@@ -4053,7 +4236,7 @@
         <v>19</v>
       </c>
       <c r="B324" t="s" s="0">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="325">
@@ -4081,13 +4264,13 @@
         <v>1.0</v>
       </c>
       <c r="B326" t="s" s="3">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C326" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D326" t="s" s="3">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E326" t="s" s="3">
         <v>28</v>
@@ -4109,7 +4292,7 @@
         <v>2</v>
       </c>
       <c r="B330" t="s" s="0">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C330" t="s" s="1">
         <v>10</v>
@@ -4148,7 +4331,7 @@
         <v>19</v>
       </c>
       <c r="B333" t="s" s="0">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="334">
@@ -4176,7 +4359,7 @@
         <v>1.0</v>
       </c>
       <c r="B335" t="s" s="3">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C335" t="s" s="3">
         <v>28</v>
@@ -4204,7 +4387,7 @@
         <v>2</v>
       </c>
       <c r="B339" t="s" s="0">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C339" t="s" s="1">
         <v>10</v>
@@ -4232,7 +4415,7 @@
         <v>16</v>
       </c>
       <c r="B341" t="s" s="0">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E341" t="s" s="1">
         <v>18</v>
@@ -4243,7 +4426,7 @@
         <v>19</v>
       </c>
       <c r="B342" t="s" s="0">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="343">
@@ -4271,7 +4454,7 @@
         <v>1.0</v>
       </c>
       <c r="B344" t="s" s="3">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C344" t="s" s="3">
         <v>28</v>
@@ -4299,7 +4482,7 @@
         <v>2</v>
       </c>
       <c r="B348" t="s" s="0">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C348" t="s" s="1">
         <v>10</v>
@@ -4327,7 +4510,7 @@
         <v>16</v>
       </c>
       <c r="B350" t="s" s="0">
-        <v>121</v>
+        <v>42</v>
       </c>
       <c r="E350" t="s" s="1">
         <v>18</v>
@@ -4338,7 +4521,7 @@
         <v>19</v>
       </c>
       <c r="B351" t="s" s="0">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="352">
@@ -4366,13 +4549,13 @@
         <v>1.0</v>
       </c>
       <c r="B353" t="s" s="3">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C353" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D353" t="s" s="3">
-        <v>48</v>
+        <v>124</v>
       </c>
       <c r="E353" t="s" s="3">
         <v>28</v>
@@ -4386,7 +4569,7 @@
         <v>30</v>
       </c>
       <c r="B354" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="357">
@@ -4394,7 +4577,7 @@
         <v>2</v>
       </c>
       <c r="B357" t="s" s="0">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C357" t="s" s="1">
         <v>10</v>
@@ -4408,7 +4591,7 @@
         <v>12</v>
       </c>
       <c r="B358" t="s" s="0">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C358" t="s" s="1">
         <v>14</v>
@@ -4422,7 +4605,7 @@
         <v>16</v>
       </c>
       <c r="B359" t="s" s="0">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="E359" t="s" s="1">
         <v>18</v>
@@ -4433,7 +4616,7 @@
         <v>19</v>
       </c>
       <c r="B360" t="s" s="0">
-        <v>107</v>
+        <v>126</v>
       </c>
     </row>
     <row r="361">
@@ -4461,13 +4644,13 @@
         <v>1.0</v>
       </c>
       <c r="B362" t="s" s="3">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C362" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D362" t="s" s="3">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E362" t="s" s="3">
         <v>28</v>
@@ -4481,7 +4664,7 @@
         <v>30</v>
       </c>
       <c r="B363" t="s" s="0">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="366">
@@ -4489,7 +4672,7 @@
         <v>2</v>
       </c>
       <c r="B366" t="s" s="0">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C366" t="s" s="1">
         <v>10</v>
@@ -4503,7 +4686,7 @@
         <v>12</v>
       </c>
       <c r="B367" t="s" s="0">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C367" t="s" s="1">
         <v>14</v>
@@ -4517,7 +4700,7 @@
         <v>16</v>
       </c>
       <c r="B368" t="s" s="0">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c r="E368" t="s" s="1">
         <v>18</v>
@@ -4528,7 +4711,7 @@
         <v>19</v>
       </c>
       <c r="B369" t="s" s="0">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="370">
@@ -4556,13 +4739,13 @@
         <v>1.0</v>
       </c>
       <c r="B371" t="s" s="3">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C371" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D371" t="s" s="3">
-        <v>48</v>
+        <v>128</v>
       </c>
       <c r="E371" t="s" s="3">
         <v>28</v>
@@ -4576,7 +4759,7 @@
         <v>30</v>
       </c>
       <c r="B372" t="s" s="0">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="375">
@@ -4584,7 +4767,7 @@
         <v>2</v>
       </c>
       <c r="B375" t="s" s="0">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C375" t="s" s="1">
         <v>10</v>
@@ -4598,7 +4781,7 @@
         <v>12</v>
       </c>
       <c r="B376" t="s" s="0">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C376" t="s" s="1">
         <v>14</v>
@@ -4612,7 +4795,7 @@
         <v>16</v>
       </c>
       <c r="B377" t="s" s="0">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E377" t="s" s="1">
         <v>18</v>
@@ -4623,7 +4806,7 @@
         <v>19</v>
       </c>
       <c r="B378" t="s" s="0">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="379">
@@ -4651,13 +4834,13 @@
         <v>1.0</v>
       </c>
       <c r="B380" t="s" s="3">
+        <v>132</v>
+      </c>
+      <c r="C380" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D380" t="s" s="3">
         <v>128</v>
-      </c>
-      <c r="C380" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="D380" t="s" s="3">
-        <v>48</v>
       </c>
       <c r="E380" t="s" s="3">
         <v>28</v>
@@ -4671,7 +4854,7 @@
         <v>30</v>
       </c>
       <c r="B381" t="s" s="0">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="384">
@@ -4679,7 +4862,7 @@
         <v>2</v>
       </c>
       <c r="B384" t="s" s="0">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C384" t="s" s="1">
         <v>10</v>
@@ -4693,7 +4876,7 @@
         <v>12</v>
       </c>
       <c r="B385" t="s" s="0">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C385" t="s" s="1">
         <v>14</v>
@@ -4707,7 +4890,7 @@
         <v>16</v>
       </c>
       <c r="B386" t="s" s="0">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E386" t="s" s="1">
         <v>18</v>
@@ -4718,7 +4901,7 @@
         <v>19</v>
       </c>
       <c r="B387" t="s" s="0">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="388">
@@ -4746,13 +4929,13 @@
         <v>1.0</v>
       </c>
       <c r="B389" t="s" s="3">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C389" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D389" t="s" s="3">
-        <v>48</v>
+        <v>128</v>
       </c>
       <c r="E389" t="s" s="3">
         <v>28</v>
@@ -4766,7 +4949,7 @@
         <v>30</v>
       </c>
       <c r="B390" t="s" s="0">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="393">
@@ -4774,7 +4957,7 @@
         <v>2</v>
       </c>
       <c r="B393" t="s" s="0">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C393" t="s" s="1">
         <v>10</v>
@@ -4788,7 +4971,7 @@
         <v>12</v>
       </c>
       <c r="B394" t="s" s="0">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C394" t="s" s="1">
         <v>14</v>
@@ -4802,7 +4985,7 @@
         <v>16</v>
       </c>
       <c r="B395" t="s" s="0">
-        <v>131</v>
+        <v>42</v>
       </c>
       <c r="E395" t="s" s="1">
         <v>18</v>
@@ -4813,7 +4996,7 @@
         <v>19</v>
       </c>
       <c r="B396" t="s" s="0">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="397">
@@ -4841,13 +5024,13 @@
         <v>1.0</v>
       </c>
       <c r="B398" t="s" s="3">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C398" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D398" t="s" s="3">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="E398" t="s" s="3">
         <v>28</v>
@@ -4861,7 +5044,7 @@
         <v>30</v>
       </c>
       <c r="B399" t="s" s="0">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="402">
@@ -4869,7 +5052,7 @@
         <v>2</v>
       </c>
       <c r="B402" t="s" s="0">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C402" t="s" s="1">
         <v>10</v>
@@ -4883,7 +5066,7 @@
         <v>12</v>
       </c>
       <c r="B403" t="s" s="0">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C403" t="s" s="1">
         <v>14</v>
@@ -4897,7 +5080,7 @@
         <v>16</v>
       </c>
       <c r="B404" t="s" s="0">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="E404" t="s" s="1">
         <v>18</v>
@@ -4908,7 +5091,7 @@
         <v>19</v>
       </c>
       <c r="B405" t="s" s="0">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="406">
@@ -4936,7 +5119,7 @@
         <v>1.0</v>
       </c>
       <c r="B407" t="s" s="3">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C407" t="s" s="3">
         <v>28</v>
@@ -4956,7 +5139,7 @@
         <v>30</v>
       </c>
       <c r="B408" t="s" s="0">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="411">
@@ -4964,7 +5147,7 @@
         <v>2</v>
       </c>
       <c r="B411" t="s" s="0">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C411" t="s" s="1">
         <v>10</v>
@@ -4978,7 +5161,7 @@
         <v>12</v>
       </c>
       <c r="B412" t="s" s="0">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C412" t="s" s="1">
         <v>14</v>
@@ -4992,7 +5175,7 @@
         <v>16</v>
       </c>
       <c r="B413" t="s" s="0">
-        <v>42</v>
+        <v>138</v>
       </c>
       <c r="E413" t="s" s="1">
         <v>18</v>
@@ -5003,7 +5186,7 @@
         <v>19</v>
       </c>
       <c r="B414" t="s" s="0">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="415">
@@ -5031,13 +5214,13 @@
         <v>1.0</v>
       </c>
       <c r="B416" t="s" s="3">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="C416" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D416" t="s" s="3">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="E416" t="s" s="3">
         <v>28</v>
@@ -5051,7 +5234,7 @@
         <v>30</v>
       </c>
       <c r="B417" t="s" s="0">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="420">
@@ -5073,7 +5256,7 @@
         <v>12</v>
       </c>
       <c r="B421" t="s" s="0">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C421" t="s" s="1">
         <v>14</v>
@@ -5087,7 +5270,7 @@
         <v>16</v>
       </c>
       <c r="B422" t="s" s="0">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="E422" t="s" s="1">
         <v>18</v>
@@ -5098,7 +5281,7 @@
         <v>19</v>
       </c>
       <c r="B423" t="s" s="0">
-        <v>137</v>
+        <v>126</v>
       </c>
     </row>
     <row r="424">
@@ -5126,7 +5309,7 @@
         <v>1.0</v>
       </c>
       <c r="B425" t="s" s="3">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C425" t="s" s="3">
         <v>28</v>
@@ -5168,7 +5351,7 @@
         <v>12</v>
       </c>
       <c r="B430" t="s" s="0">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C430" t="s" s="1">
         <v>14</v>
@@ -5182,7 +5365,7 @@
         <v>16</v>
       </c>
       <c r="B431" t="s" s="0">
-        <v>139</v>
+        <v>42</v>
       </c>
       <c r="E431" t="s" s="1">
         <v>18</v>
@@ -5193,7 +5376,7 @@
         <v>19</v>
       </c>
       <c r="B432" t="s" s="0">
-        <v>137</v>
+        <v>126</v>
       </c>
     </row>
     <row r="433">
@@ -5221,13 +5404,13 @@
         <v>1.0</v>
       </c>
       <c r="B434" t="s" s="3">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C434" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D434" t="s" s="3">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="E434" t="s" s="3">
         <v>28</v>
@@ -5241,7 +5424,7 @@
         <v>30</v>
       </c>
       <c r="B435" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="438">
@@ -5249,7 +5432,7 @@
         <v>2</v>
       </c>
       <c r="B438" t="s" s="0">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C438" t="s" s="1">
         <v>10</v>
@@ -5263,7 +5446,7 @@
         <v>12</v>
       </c>
       <c r="B439" t="s" s="0">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C439" t="s" s="1">
         <v>14</v>
@@ -5277,7 +5460,7 @@
         <v>16</v>
       </c>
       <c r="B440" t="s" s="0">
-        <v>141</v>
+        <v>17</v>
       </c>
       <c r="E440" t="s" s="1">
         <v>18</v>
@@ -5288,7 +5471,7 @@
         <v>19</v>
       </c>
       <c r="B441" t="s" s="0">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="442">
@@ -5316,7 +5499,7 @@
         <v>1.0</v>
       </c>
       <c r="B443" t="s" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C443" t="s" s="3">
         <v>28</v>
@@ -5336,7 +5519,7 @@
         <v>30</v>
       </c>
       <c r="B444" t="s" s="0">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="447">
@@ -5344,7 +5527,7 @@
         <v>2</v>
       </c>
       <c r="B447" t="s" s="0">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C447" t="s" s="1">
         <v>10</v>
@@ -5358,7 +5541,7 @@
         <v>12</v>
       </c>
       <c r="B448" t="s" s="0">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C448" t="s" s="1">
         <v>14</v>
@@ -5372,7 +5555,7 @@
         <v>16</v>
       </c>
       <c r="B449" t="s" s="0">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E449" t="s" s="1">
         <v>18</v>
@@ -5383,7 +5566,7 @@
         <v>19</v>
       </c>
       <c r="B450" t="s" s="0">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="451">
@@ -5411,7 +5594,7 @@
         <v>1.0</v>
       </c>
       <c r="B452" t="s" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C452" t="s" s="3">
         <v>28</v>
@@ -5431,7 +5614,7 @@
         <v>30</v>
       </c>
       <c r="B453" t="s" s="0">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="456">
@@ -5439,7 +5622,7 @@
         <v>2</v>
       </c>
       <c r="B456" t="s" s="0">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C456" t="s" s="1">
         <v>10</v>
@@ -5453,7 +5636,7 @@
         <v>12</v>
       </c>
       <c r="B457" t="s" s="0">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C457" t="s" s="1">
         <v>14</v>
@@ -5467,7 +5650,7 @@
         <v>16</v>
       </c>
       <c r="B458" t="s" s="0">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E458" t="s" s="1">
         <v>18</v>
@@ -5478,7 +5661,7 @@
         <v>19</v>
       </c>
       <c r="B459" t="s" s="0">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="460">
@@ -5506,7 +5689,7 @@
         <v>1.0</v>
       </c>
       <c r="B461" t="s" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C461" t="s" s="3">
         <v>28</v>
@@ -5526,7 +5709,7 @@
         <v>30</v>
       </c>
       <c r="B462" t="s" s="0">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="465">
@@ -5534,7 +5717,7 @@
         <v>2</v>
       </c>
       <c r="B465" t="s" s="0">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C465" t="s" s="1">
         <v>10</v>
@@ -5548,7 +5731,7 @@
         <v>12</v>
       </c>
       <c r="B466" t="s" s="0">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="C466" t="s" s="1">
         <v>14</v>
@@ -5562,7 +5745,7 @@
         <v>16</v>
       </c>
       <c r="B467" t="s" s="0">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E467" t="s" s="1">
         <v>18</v>
@@ -5573,7 +5756,7 @@
         <v>19</v>
       </c>
       <c r="B468" t="s" s="0">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="469">
@@ -5601,7 +5784,7 @@
         <v>1.0</v>
       </c>
       <c r="B470" t="s" s="3">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C470" t="s" s="3">
         <v>28</v>
@@ -5621,7 +5804,7 @@
         <v>30</v>
       </c>
       <c r="B471" t="s" s="0">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="474">
@@ -5629,7 +5812,7 @@
         <v>2</v>
       </c>
       <c r="B474" t="s" s="0">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C474" t="s" s="1">
         <v>10</v>
@@ -5643,7 +5826,7 @@
         <v>12</v>
       </c>
       <c r="B475" t="s" s="0">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="C475" t="s" s="1">
         <v>14</v>
@@ -5657,7 +5840,7 @@
         <v>16</v>
       </c>
       <c r="B476" t="s" s="0">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E476" t="s" s="1">
         <v>18</v>
@@ -5668,7 +5851,7 @@
         <v>19</v>
       </c>
       <c r="B477" t="s" s="0">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="478">
@@ -5696,7 +5879,7 @@
         <v>1.0</v>
       </c>
       <c r="B479" t="s" s="3">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C479" t="s" s="3">
         <v>28</v>
@@ -5716,7 +5899,7 @@
         <v>30</v>
       </c>
       <c r="B480" t="s" s="0">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="483">
@@ -5724,7 +5907,7 @@
         <v>2</v>
       </c>
       <c r="B483" t="s" s="0">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C483" t="s" s="1">
         <v>10</v>
@@ -5738,7 +5921,7 @@
         <v>12</v>
       </c>
       <c r="B484" t="s" s="0">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="C484" t="s" s="1">
         <v>14</v>
@@ -5752,7 +5935,7 @@
         <v>16</v>
       </c>
       <c r="B485" t="s" s="0">
-        <v>152</v>
+        <v>42</v>
       </c>
       <c r="E485" t="s" s="1">
         <v>18</v>
@@ -5763,7 +5946,7 @@
         <v>19</v>
       </c>
       <c r="B486" t="s" s="0">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="487">
@@ -5791,13 +5974,13 @@
         <v>1.0</v>
       </c>
       <c r="B488" t="s" s="3">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C488" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D488" t="s" s="3">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="E488" t="s" s="3">
         <v>28</v>
@@ -5811,7 +5994,7 @@
         <v>30</v>
       </c>
       <c r="B489" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="492">
@@ -5819,7 +6002,7 @@
         <v>2</v>
       </c>
       <c r="B492" t="s" s="0">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="C492" t="s" s="1">
         <v>10</v>
@@ -5833,7 +6016,7 @@
         <v>12</v>
       </c>
       <c r="B493" t="s" s="0">
-        <v>154</v>
+        <v>13</v>
       </c>
       <c r="C493" t="s" s="1">
         <v>14</v>
@@ -5847,7 +6030,7 @@
         <v>16</v>
       </c>
       <c r="B494" t="s" s="0">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="E494" t="s" s="1">
         <v>18</v>
@@ -5858,7 +6041,7 @@
         <v>19</v>
       </c>
       <c r="B495" t="s" s="0">
-        <v>137</v>
+        <v>156</v>
       </c>
     </row>
     <row r="496">
@@ -5886,13 +6069,13 @@
         <v>1.0</v>
       </c>
       <c r="B497" t="s" s="3">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="C497" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D497" t="s" s="3">
-        <v>155</v>
+        <v>48</v>
       </c>
       <c r="E497" t="s" s="3">
         <v>28</v>
@@ -5906,7 +6089,7 @@
         <v>30</v>
       </c>
       <c r="B498" t="s" s="0">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="501">
@@ -5914,7 +6097,7 @@
         <v>2</v>
       </c>
       <c r="B501" t="s" s="0">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="C501" t="s" s="1">
         <v>10</v>
@@ -5928,7 +6111,7 @@
         <v>12</v>
       </c>
       <c r="B502" t="s" s="0">
-        <v>156</v>
+        <v>32</v>
       </c>
       <c r="C502" t="s" s="1">
         <v>14</v>
@@ -5942,7 +6125,7 @@
         <v>16</v>
       </c>
       <c r="B503" t="s" s="0">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E503" t="s" s="1">
         <v>18</v>
@@ -5953,7 +6136,7 @@
         <v>19</v>
       </c>
       <c r="B504" t="s" s="0">
-        <v>137</v>
+        <v>156</v>
       </c>
     </row>
     <row r="505">
@@ -5981,13 +6164,13 @@
         <v>1.0</v>
       </c>
       <c r="B506" t="s" s="3">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="C506" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D506" t="s" s="3">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="E506" t="s" s="3">
         <v>28</v>
@@ -6001,7 +6184,7 @@
         <v>30</v>
       </c>
       <c r="B507" t="s" s="0">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="510">
@@ -6009,13 +6192,13 @@
         <v>2</v>
       </c>
       <c r="B510" t="s" s="0">
-        <v>9</v>
+        <v>155</v>
       </c>
       <c r="C510" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D510" t="s" s="0">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="511">
@@ -6023,7 +6206,7 @@
         <v>12</v>
       </c>
       <c r="B511" t="s" s="0">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C511" t="s" s="1">
         <v>14</v>
@@ -6037,7 +6220,7 @@
         <v>16</v>
       </c>
       <c r="B512" t="s" s="0">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="E512" t="s" s="1">
         <v>18</v>
@@ -6048,7 +6231,7 @@
         <v>19</v>
       </c>
       <c r="B513" t="s" s="0">
-        <v>20</v>
+        <v>156</v>
       </c>
     </row>
     <row r="514">
@@ -6076,13 +6259,13 @@
         <v>1.0</v>
       </c>
       <c r="B515" t="s" s="3">
-        <v>27</v>
+        <v>161</v>
       </c>
       <c r="C515" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D515" t="s" s="3">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="E515" t="s" s="3">
         <v>28</v>
@@ -6096,7 +6279,7 @@
         <v>30</v>
       </c>
       <c r="B516" t="s" s="0">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="519">
@@ -6104,13 +6287,13 @@
         <v>2</v>
       </c>
       <c r="B519" t="s" s="0">
-        <v>9</v>
+        <v>155</v>
       </c>
       <c r="C519" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D519" t="s" s="0">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="520">
@@ -6118,7 +6301,7 @@
         <v>12</v>
       </c>
       <c r="B520" t="s" s="0">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C520" t="s" s="1">
         <v>14</v>
@@ -6132,7 +6315,7 @@
         <v>16</v>
       </c>
       <c r="B521" t="s" s="0">
-        <v>33</v>
+        <v>162</v>
       </c>
       <c r="E521" t="s" s="1">
         <v>18</v>
@@ -6143,7 +6326,7 @@
         <v>19</v>
       </c>
       <c r="B522" t="s" s="0">
-        <v>20</v>
+        <v>156</v>
       </c>
     </row>
     <row r="523">
@@ -6171,13 +6354,13 @@
         <v>1.0</v>
       </c>
       <c r="B524" t="s" s="3">
-        <v>34</v>
+        <v>163</v>
       </c>
       <c r="C524" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D524" t="s" s="3">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="E524" t="s" s="3">
         <v>28</v>
@@ -6191,7 +6374,7 @@
         <v>30</v>
       </c>
       <c r="B525" t="s" s="0">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="528">
@@ -6199,13 +6382,13 @@
         <v>2</v>
       </c>
       <c r="B528" t="s" s="0">
-        <v>9</v>
+        <v>155</v>
       </c>
       <c r="C528" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D528" t="s" s="0">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="529">
@@ -6213,7 +6396,7 @@
         <v>12</v>
       </c>
       <c r="B529" t="s" s="0">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C529" t="s" s="1">
         <v>14</v>
@@ -6227,7 +6410,7 @@
         <v>16</v>
       </c>
       <c r="B530" t="s" s="0">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="E530" t="s" s="1">
         <v>18</v>
@@ -6238,7 +6421,7 @@
         <v>19</v>
       </c>
       <c r="B531" t="s" s="0">
-        <v>20</v>
+        <v>156</v>
       </c>
     </row>
     <row r="532">
@@ -6266,13 +6449,13 @@
         <v>1.0</v>
       </c>
       <c r="B533" t="s" s="3">
-        <v>37</v>
+        <v>165</v>
       </c>
       <c r="C533" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D533" t="s" s="3">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="E533" t="s" s="3">
         <v>28</v>
@@ -6286,7 +6469,7 @@
         <v>30</v>
       </c>
       <c r="B534" t="s" s="0">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="537">
@@ -6294,13 +6477,13 @@
         <v>2</v>
       </c>
       <c r="B537" t="s" s="0">
-        <v>9</v>
+        <v>155</v>
       </c>
       <c r="C537" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D537" t="s" s="0">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="538">
@@ -6308,7 +6491,7 @@
         <v>12</v>
       </c>
       <c r="B538" t="s" s="0">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C538" t="s" s="1">
         <v>14</v>
@@ -6322,7 +6505,7 @@
         <v>16</v>
       </c>
       <c r="B539" t="s" s="0">
-        <v>39</v>
+        <v>166</v>
       </c>
       <c r="E539" t="s" s="1">
         <v>18</v>
@@ -6333,7 +6516,7 @@
         <v>19</v>
       </c>
       <c r="B540" t="s" s="0">
-        <v>20</v>
+        <v>156</v>
       </c>
     </row>
     <row r="541">
@@ -6361,13 +6544,13 @@
         <v>1.0</v>
       </c>
       <c r="B542" t="s" s="3">
-        <v>40</v>
+        <v>167</v>
       </c>
       <c r="C542" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D542" t="s" s="3">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="E542" t="s" s="3">
         <v>28</v>
@@ -6381,7 +6564,7 @@
         <v>30</v>
       </c>
       <c r="B543" t="s" s="0">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="546">
@@ -6389,13 +6572,13 @@
         <v>2</v>
       </c>
       <c r="B546" t="s" s="0">
-        <v>9</v>
+        <v>155</v>
       </c>
       <c r="C546" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D546" t="s" s="0">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="547">
@@ -6403,7 +6586,7 @@
         <v>12</v>
       </c>
       <c r="B547" t="s" s="0">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="C547" t="s" s="1">
         <v>14</v>
@@ -6417,7 +6600,7 @@
         <v>16</v>
       </c>
       <c r="B548" t="s" s="0">
-        <v>42</v>
+        <v>168</v>
       </c>
       <c r="E548" t="s" s="1">
         <v>18</v>
@@ -6428,7 +6611,7 @@
         <v>19</v>
       </c>
       <c r="B549" t="s" s="0">
-        <v>20</v>
+        <v>156</v>
       </c>
     </row>
     <row r="550">
@@ -6456,13 +6639,13 @@
         <v>1.0</v>
       </c>
       <c r="B551" t="s" s="3">
-        <v>27</v>
+        <v>169</v>
       </c>
       <c r="C551" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D551" t="s" s="3">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E551" t="s" s="3">
         <v>28</v>
@@ -6476,7 +6659,7 @@
         <v>30</v>
       </c>
       <c r="B552" t="s" s="0">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="555">
@@ -6484,13 +6667,13 @@
         <v>2</v>
       </c>
       <c r="B555" t="s" s="0">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="C555" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D555" t="s" s="0">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="556">
@@ -6498,7 +6681,7 @@
         <v>12</v>
       </c>
       <c r="B556" t="s" s="0">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="C556" t="s" s="1">
         <v>14</v>
@@ -6512,7 +6695,7 @@
         <v>16</v>
       </c>
       <c r="B557" t="s" s="0">
-        <v>17</v>
+        <v>171</v>
       </c>
       <c r="E557" t="s" s="1">
         <v>18</v>
@@ -6523,7 +6706,7 @@
         <v>19</v>
       </c>
       <c r="B558" t="s" s="0">
-        <v>46</v>
+        <v>156</v>
       </c>
     </row>
     <row r="559">
@@ -6551,7 +6734,7 @@
         <v>1.0</v>
       </c>
       <c r="B560" t="s" s="3">
-        <v>47</v>
+        <v>172</v>
       </c>
       <c r="C560" t="s" s="3">
         <v>28</v>
@@ -6579,13 +6762,13 @@
         <v>2</v>
       </c>
       <c r="B564" t="s" s="0">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="C564" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D564" t="s" s="0">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="565">
@@ -6593,7 +6776,7 @@
         <v>12</v>
       </c>
       <c r="B565" t="s" s="0">
-        <v>32</v>
+        <v>173</v>
       </c>
       <c r="C565" t="s" s="1">
         <v>14</v>
@@ -6607,7 +6790,7 @@
         <v>16</v>
       </c>
       <c r="B566" t="s" s="0">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E566" t="s" s="1">
         <v>18</v>
@@ -6618,7 +6801,7 @@
         <v>19</v>
       </c>
       <c r="B567" t="s" s="0">
-        <v>46</v>
+        <v>156</v>
       </c>
     </row>
     <row r="568">
@@ -6646,13 +6829,13 @@
         <v>1.0</v>
       </c>
       <c r="B569" t="s" s="3">
-        <v>51</v>
+        <v>157</v>
       </c>
       <c r="C569" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D569" t="s" s="3">
-        <v>48</v>
+        <v>174</v>
       </c>
       <c r="E569" t="s" s="3">
         <v>28</v>
@@ -6666,7 +6849,7 @@
         <v>30</v>
       </c>
       <c r="B570" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="573">
@@ -6674,13 +6857,13 @@
         <v>2</v>
       </c>
       <c r="B573" t="s" s="0">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="C573" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D573" t="s" s="0">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="574">
@@ -6688,7 +6871,7 @@
         <v>12</v>
       </c>
       <c r="B574" t="s" s="0">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="C574" t="s" s="1">
         <v>14</v>
@@ -6702,7 +6885,7 @@
         <v>16</v>
       </c>
       <c r="B575" t="s" s="0">
-        <v>52</v>
+        <v>176</v>
       </c>
       <c r="E575" t="s" s="1">
         <v>18</v>
@@ -6713,7 +6896,7 @@
         <v>19</v>
       </c>
       <c r="B576" t="s" s="0">
-        <v>46</v>
+        <v>156</v>
       </c>
     </row>
     <row r="577">
@@ -6741,13 +6924,13 @@
         <v>1.0</v>
       </c>
       <c r="B578" t="s" s="3">
-        <v>47</v>
+        <v>157</v>
       </c>
       <c r="C578" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D578" t="s" s="3">
-        <v>53</v>
+        <v>177</v>
       </c>
       <c r="E578" t="s" s="3">
         <v>28</v>
@@ -6769,13 +6952,13 @@
         <v>2</v>
       </c>
       <c r="B582" t="s" s="0">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="C582" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D582" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="583">
@@ -6783,7 +6966,7 @@
         <v>12</v>
       </c>
       <c r="B583" t="s" s="0">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C583" t="s" s="1">
         <v>14</v>
@@ -6797,7 +6980,7 @@
         <v>16</v>
       </c>
       <c r="B584" t="s" s="0">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="E584" t="s" s="1">
         <v>18</v>
@@ -6808,7 +6991,7 @@
         <v>19</v>
       </c>
       <c r="B585" t="s" s="0">
-        <v>46</v>
+        <v>20</v>
       </c>
     </row>
     <row r="586">
@@ -6836,13 +7019,13 @@
         <v>1.0</v>
       </c>
       <c r="B587" t="s" s="3">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C587" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D587" t="s" s="3">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="E587" t="s" s="3">
         <v>28</v>
@@ -6856,7 +7039,7 @@
         <v>30</v>
       </c>
       <c r="B588" t="s" s="0">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="591">
@@ -6864,13 +7047,13 @@
         <v>2</v>
       </c>
       <c r="B591" t="s" s="0">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="C591" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D591" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="592">
@@ -6878,7 +7061,7 @@
         <v>12</v>
       </c>
       <c r="B592" t="s" s="0">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C592" t="s" s="1">
         <v>14</v>
@@ -6892,7 +7075,7 @@
         <v>16</v>
       </c>
       <c r="B593" t="s" s="0">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="E593" t="s" s="1">
         <v>18</v>
@@ -6903,7 +7086,7 @@
         <v>19</v>
       </c>
       <c r="B594" t="s" s="0">
-        <v>46</v>
+        <v>20</v>
       </c>
     </row>
     <row r="595">
@@ -6931,13 +7114,13 @@
         <v>1.0</v>
       </c>
       <c r="B596" t="s" s="3">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C596" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D596" t="s" s="3">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="E596" t="s" s="3">
         <v>28</v>
@@ -6951,7 +7134,7 @@
         <v>30</v>
       </c>
       <c r="B597" t="s" s="0">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="600">
@@ -6959,13 +7142,13 @@
         <v>2</v>
       </c>
       <c r="B600" t="s" s="0">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="C600" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D600" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="601">
@@ -6973,7 +7156,7 @@
         <v>12</v>
       </c>
       <c r="B601" t="s" s="0">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="C601" t="s" s="1">
         <v>14</v>
@@ -6987,7 +7170,7 @@
         <v>16</v>
       </c>
       <c r="B602" t="s" s="0">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E602" t="s" s="1">
         <v>18</v>
@@ -6998,7 +7181,7 @@
         <v>19</v>
       </c>
       <c r="B603" t="s" s="0">
-        <v>46</v>
+        <v>20</v>
       </c>
     </row>
     <row r="604">
@@ -7026,13 +7209,13 @@
         <v>1.0</v>
       </c>
       <c r="B605" t="s" s="3">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C605" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D605" t="s" s="3">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="E605" t="s" s="3">
         <v>28</v>
@@ -7046,7 +7229,7 @@
         <v>30</v>
       </c>
       <c r="B606" t="s" s="0">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="609">
@@ -7054,13 +7237,13 @@
         <v>2</v>
       </c>
       <c r="B609" t="s" s="0">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="C609" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D609" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="610">
@@ -7068,7 +7251,7 @@
         <v>12</v>
       </c>
       <c r="B610" t="s" s="0">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="C610" t="s" s="1">
         <v>14</v>
@@ -7082,7 +7265,7 @@
         <v>16</v>
       </c>
       <c r="B611" t="s" s="0">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="E611" t="s" s="1">
         <v>18</v>
@@ -7093,7 +7276,7 @@
         <v>19</v>
       </c>
       <c r="B612" t="s" s="0">
-        <v>46</v>
+        <v>20</v>
       </c>
     </row>
     <row r="613">
@@ -7121,13 +7304,13 @@
         <v>1.0</v>
       </c>
       <c r="B614" t="s" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C614" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D614" t="s" s="3">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="E614" t="s" s="3">
         <v>28</v>
@@ -7141,7 +7324,7 @@
         <v>30</v>
       </c>
       <c r="B615" t="s" s="0">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="618">
@@ -7149,13 +7332,13 @@
         <v>2</v>
       </c>
       <c r="B618" t="s" s="0">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="C618" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D618" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="619">
@@ -7163,7 +7346,7 @@
         <v>12</v>
       </c>
       <c r="B619" t="s" s="0">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="C619" t="s" s="1">
         <v>14</v>
@@ -7177,7 +7360,7 @@
         <v>16</v>
       </c>
       <c r="B620" t="s" s="0">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="E620" t="s" s="1">
         <v>18</v>
@@ -7188,7 +7371,7 @@
         <v>19</v>
       </c>
       <c r="B621" t="s" s="0">
-        <v>65</v>
+        <v>20</v>
       </c>
     </row>
     <row r="622">
@@ -7216,13 +7399,13 @@
         <v>1.0</v>
       </c>
       <c r="B623" t="s" s="3">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C623" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D623" t="s" s="3">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="E623" t="s" s="3">
         <v>28</v>
@@ -7236,7 +7419,7 @@
         <v>30</v>
       </c>
       <c r="B624" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="627">
@@ -7244,13 +7427,13 @@
         <v>2</v>
       </c>
       <c r="B627" t="s" s="0">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C627" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D627" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="628">
@@ -7258,7 +7441,7 @@
         <v>12</v>
       </c>
       <c r="B628" t="s" s="0">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C628" t="s" s="1">
         <v>14</v>
@@ -7272,7 +7455,7 @@
         <v>16</v>
       </c>
       <c r="B629" t="s" s="0">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="E629" t="s" s="1">
         <v>18</v>
@@ -7283,7 +7466,7 @@
         <v>19</v>
       </c>
       <c r="B630" t="s" s="0">
-        <v>65</v>
+        <v>46</v>
       </c>
     </row>
     <row r="631">
@@ -7311,13 +7494,13 @@
         <v>1.0</v>
       </c>
       <c r="B632" t="s" s="3">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="C632" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D632" t="s" s="3">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="E632" t="s" s="3">
         <v>28</v>
@@ -7331,7 +7514,7 @@
         <v>30</v>
       </c>
       <c r="B633" t="s" s="0">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="636">
@@ -7339,13 +7522,13 @@
         <v>2</v>
       </c>
       <c r="B636" t="s" s="0">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C636" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D636" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="637">
@@ -7353,7 +7536,7 @@
         <v>12</v>
       </c>
       <c r="B637" t="s" s="0">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C637" t="s" s="1">
         <v>14</v>
@@ -7367,7 +7550,7 @@
         <v>16</v>
       </c>
       <c r="B638" t="s" s="0">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E638" t="s" s="1">
         <v>18</v>
@@ -7378,7 +7561,7 @@
         <v>19</v>
       </c>
       <c r="B639" t="s" s="0">
-        <v>65</v>
+        <v>46</v>
       </c>
     </row>
     <row r="640">
@@ -7406,13 +7589,13 @@
         <v>1.0</v>
       </c>
       <c r="B641" t="s" s="3">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C641" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D641" t="s" s="3">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="E641" t="s" s="3">
         <v>28</v>
@@ -7426,7 +7609,7 @@
         <v>30</v>
       </c>
       <c r="B642" t="s" s="0">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="645">
@@ -7434,13 +7617,13 @@
         <v>2</v>
       </c>
       <c r="B645" t="s" s="0">
-        <v>160</v>
+        <v>45</v>
       </c>
       <c r="C645" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D645" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="646">
@@ -7448,7 +7631,7 @@
         <v>12</v>
       </c>
       <c r="B646" t="s" s="0">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C646" t="s" s="1">
         <v>14</v>
@@ -7462,7 +7645,7 @@
         <v>16</v>
       </c>
       <c r="B647" t="s" s="0">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="E647" t="s" s="1">
         <v>18</v>
@@ -7473,7 +7656,7 @@
         <v>19</v>
       </c>
       <c r="B648" t="s" s="0">
-        <v>161</v>
+        <v>46</v>
       </c>
     </row>
     <row r="649">
@@ -7501,13 +7684,13 @@
         <v>1.0</v>
       </c>
       <c r="B650" t="s" s="3">
-        <v>162</v>
+        <v>47</v>
       </c>
       <c r="C650" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D650" t="s" s="3">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="E650" t="s" s="3">
         <v>28</v>
@@ -7521,7 +7704,7 @@
         <v>30</v>
       </c>
       <c r="B651" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="654">
@@ -7529,13 +7712,13 @@
         <v>2</v>
       </c>
       <c r="B654" t="s" s="0">
-        <v>160</v>
+        <v>45</v>
       </c>
       <c r="C654" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D654" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="655">
@@ -7543,7 +7726,7 @@
         <v>12</v>
       </c>
       <c r="B655" t="s" s="0">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C655" t="s" s="1">
         <v>14</v>
@@ -7557,7 +7740,7 @@
         <v>16</v>
       </c>
       <c r="B656" t="s" s="0">
-        <v>164</v>
+        <v>54</v>
       </c>
       <c r="E656" t="s" s="1">
         <v>18</v>
@@ -7568,7 +7751,7 @@
         <v>19</v>
       </c>
       <c r="B657" t="s" s="0">
-        <v>161</v>
+        <v>46</v>
       </c>
     </row>
     <row r="658">
@@ -7596,13 +7779,13 @@
         <v>1.0</v>
       </c>
       <c r="B659" t="s" s="3">
-        <v>165</v>
+        <v>47</v>
       </c>
       <c r="C659" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D659" t="s" s="3">
-        <v>163</v>
+        <v>55</v>
       </c>
       <c r="E659" t="s" s="3">
         <v>28</v>
@@ -7616,7 +7799,7 @@
         <v>30</v>
       </c>
       <c r="B660" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="663">
@@ -7624,13 +7807,13 @@
         <v>2</v>
       </c>
       <c r="B663" t="s" s="0">
-        <v>160</v>
+        <v>45</v>
       </c>
       <c r="C663" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D663" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="664">
@@ -7638,7 +7821,7 @@
         <v>12</v>
       </c>
       <c r="B664" t="s" s="0">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C664" t="s" s="1">
         <v>14</v>
@@ -7652,7 +7835,7 @@
         <v>16</v>
       </c>
       <c r="B665" t="s" s="0">
-        <v>166</v>
+        <v>56</v>
       </c>
       <c r="E665" t="s" s="1">
         <v>18</v>
@@ -7663,7 +7846,7 @@
         <v>19</v>
       </c>
       <c r="B666" t="s" s="0">
-        <v>161</v>
+        <v>46</v>
       </c>
     </row>
     <row r="667">
@@ -7691,13 +7874,13 @@
         <v>1.0</v>
       </c>
       <c r="B668" t="s" s="3">
-        <v>167</v>
+        <v>47</v>
       </c>
       <c r="C668" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D668" t="s" s="3">
-        <v>163</v>
+        <v>57</v>
       </c>
       <c r="E668" t="s" s="3">
         <v>28</v>
@@ -7711,7 +7894,7 @@
         <v>30</v>
       </c>
       <c r="B669" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="672">
@@ -7719,13 +7902,13 @@
         <v>2</v>
       </c>
       <c r="B672" t="s" s="0">
-        <v>160</v>
+        <v>45</v>
       </c>
       <c r="C672" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D672" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="673">
@@ -7733,7 +7916,7 @@
         <v>12</v>
       </c>
       <c r="B673" t="s" s="0">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C673" t="s" s="1">
         <v>14</v>
@@ -7747,7 +7930,7 @@
         <v>16</v>
       </c>
       <c r="B674" t="s" s="0">
-        <v>168</v>
+        <v>59</v>
       </c>
       <c r="E674" t="s" s="1">
         <v>18</v>
@@ -7758,7 +7941,7 @@
         <v>19</v>
       </c>
       <c r="B675" t="s" s="0">
-        <v>161</v>
+        <v>46</v>
       </c>
     </row>
     <row r="676">
@@ -7786,13 +7969,13 @@
         <v>1.0</v>
       </c>
       <c r="B677" t="s" s="3">
-        <v>162</v>
+        <v>47</v>
       </c>
       <c r="C677" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D677" t="s" s="3">
-        <v>169</v>
+        <v>60</v>
       </c>
       <c r="E677" t="s" s="3">
         <v>28</v>
@@ -7814,13 +7997,13 @@
         <v>2</v>
       </c>
       <c r="B681" t="s" s="0">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="C681" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D681" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="682">
@@ -7828,7 +8011,7 @@
         <v>12</v>
       </c>
       <c r="B682" t="s" s="0">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="C682" t="s" s="1">
         <v>14</v>
@@ -7842,7 +8025,7 @@
         <v>16</v>
       </c>
       <c r="B683" t="s" s="0">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="E683" t="s" s="1">
         <v>18</v>
@@ -7853,7 +8036,7 @@
         <v>19</v>
       </c>
       <c r="B684" t="s" s="0">
-        <v>171</v>
+        <v>46</v>
       </c>
     </row>
     <row r="685">
@@ -7881,13 +8064,13 @@
         <v>1.0</v>
       </c>
       <c r="B686" t="s" s="3">
-        <v>172</v>
+        <v>47</v>
       </c>
       <c r="C686" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D686" t="s" s="3">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E686" t="s" s="3">
         <v>28</v>
@@ -7901,7 +8084,7 @@
         <v>30</v>
       </c>
       <c r="B687" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="690">
@@ -7909,13 +8092,13 @@
         <v>2</v>
       </c>
       <c r="B690" t="s" s="0">
-        <v>170</v>
+        <v>64</v>
       </c>
       <c r="C690" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D690" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="691">
@@ -7923,7 +8106,7 @@
         <v>12</v>
       </c>
       <c r="B691" t="s" s="0">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C691" t="s" s="1">
         <v>14</v>
@@ -7937,7 +8120,7 @@
         <v>16</v>
       </c>
       <c r="B692" t="s" s="0">
-        <v>173</v>
+        <v>17</v>
       </c>
       <c r="E692" t="s" s="1">
         <v>18</v>
@@ -7948,7 +8131,7 @@
         <v>19</v>
       </c>
       <c r="B693" t="s" s="0">
-        <v>171</v>
+        <v>65</v>
       </c>
     </row>
     <row r="694">
@@ -7976,13 +8159,13 @@
         <v>1.0</v>
       </c>
       <c r="B695" t="s" s="3">
-        <v>174</v>
+        <v>66</v>
       </c>
       <c r="C695" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D695" t="s" s="3">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E695" t="s" s="3">
         <v>28</v>
@@ -8004,13 +8187,13 @@
         <v>2</v>
       </c>
       <c r="B699" t="s" s="0">
-        <v>170</v>
+        <v>64</v>
       </c>
       <c r="C699" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D699" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="700">
@@ -8018,7 +8201,7 @@
         <v>12</v>
       </c>
       <c r="B700" t="s" s="0">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C700" t="s" s="1">
         <v>14</v>
@@ -8032,7 +8215,7 @@
         <v>16</v>
       </c>
       <c r="B701" t="s" s="0">
-        <v>175</v>
+        <v>68</v>
       </c>
       <c r="E701" t="s" s="1">
         <v>18</v>
@@ -8043,7 +8226,7 @@
         <v>19</v>
       </c>
       <c r="B702" t="s" s="0">
-        <v>171</v>
+        <v>65</v>
       </c>
     </row>
     <row r="703">
@@ -8071,13 +8254,13 @@
         <v>1.0</v>
       </c>
       <c r="B704" t="s" s="3">
-        <v>176</v>
+        <v>66</v>
       </c>
       <c r="C704" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D704" t="s" s="3">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E704" t="s" s="3">
         <v>28</v>
@@ -8091,7 +8274,7 @@
         <v>30</v>
       </c>
       <c r="B705" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="708">
@@ -8099,13 +8282,13 @@
         <v>2</v>
       </c>
       <c r="B708" t="s" s="0">
-        <v>170</v>
+        <v>64</v>
       </c>
       <c r="C708" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D708" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="709">
@@ -8113,7 +8296,7 @@
         <v>12</v>
       </c>
       <c r="B709" t="s" s="0">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C709" t="s" s="1">
         <v>14</v>
@@ -8127,7 +8310,7 @@
         <v>16</v>
       </c>
       <c r="B710" t="s" s="0">
-        <v>177</v>
+        <v>70</v>
       </c>
       <c r="E710" t="s" s="1">
         <v>18</v>
@@ -8138,7 +8321,7 @@
         <v>19</v>
       </c>
       <c r="B711" t="s" s="0">
-        <v>171</v>
+        <v>65</v>
       </c>
     </row>
     <row r="712">
@@ -8166,13 +8349,13 @@
         <v>1.0</v>
       </c>
       <c r="B713" t="s" s="3">
-        <v>172</v>
+        <v>66</v>
       </c>
       <c r="C713" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D713" t="s" s="3">
-        <v>178</v>
+        <v>71</v>
       </c>
       <c r="E713" t="s" s="3">
         <v>28</v>
@@ -8200,7 +8383,7 @@
         <v>10</v>
       </c>
       <c r="D717" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="718">
@@ -8267,7 +8450,7 @@
         <v>28</v>
       </c>
       <c r="D722" t="s" s="3">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="E722" t="s" s="3">
         <v>28</v>
@@ -8281,7 +8464,7 @@
         <v>30</v>
       </c>
       <c r="B723" t="s" s="0">
-        <v>75</v>
+        <v>49</v>
       </c>
     </row>
     <row r="726">
@@ -8295,7 +8478,7 @@
         <v>10</v>
       </c>
       <c r="D726" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="727">
@@ -8362,7 +8545,7 @@
         <v>28</v>
       </c>
       <c r="D731" t="s" s="3">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="E731" t="s" s="3">
         <v>28</v>
@@ -8376,7 +8559,7 @@
         <v>30</v>
       </c>
       <c r="B732" t="s" s="0">
-        <v>75</v>
+        <v>49</v>
       </c>
     </row>
     <row r="735">
@@ -8390,7 +8573,7 @@
         <v>10</v>
       </c>
       <c r="D735" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="736">
@@ -8412,7 +8595,7 @@
         <v>16</v>
       </c>
       <c r="B737" t="s" s="0">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="E737" t="s" s="1">
         <v>18</v>
@@ -8451,13 +8634,13 @@
         <v>1.0</v>
       </c>
       <c r="B740" t="s" s="3">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C740" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D740" t="s" s="3">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E740" t="s" s="3">
         <v>28</v>
@@ -8471,7 +8654,7 @@
         <v>30</v>
       </c>
       <c r="B741" t="s" s="0">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="744">
@@ -8485,7 +8668,7 @@
         <v>10</v>
       </c>
       <c r="D744" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="745">
@@ -8507,7 +8690,7 @@
         <v>16</v>
       </c>
       <c r="B746" t="s" s="0">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="E746" t="s" s="1">
         <v>18</v>
@@ -8552,7 +8735,7 @@
         <v>28</v>
       </c>
       <c r="D749" t="s" s="3">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E749" t="s" s="3">
         <v>28</v>
@@ -8574,13 +8757,13 @@
         <v>2</v>
       </c>
       <c r="B753" t="s" s="0">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C753" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D753" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="754">
@@ -8613,7 +8796,7 @@
         <v>19</v>
       </c>
       <c r="B756" t="s" s="0">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="757">
@@ -8641,7 +8824,7 @@
         <v>1.0</v>
       </c>
       <c r="B758" t="s" s="3">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C758" t="s" s="3">
         <v>28</v>
@@ -8669,13 +8852,13 @@
         <v>2</v>
       </c>
       <c r="B762" t="s" s="0">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C762" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D762" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="763">
@@ -8697,7 +8880,7 @@
         <v>16</v>
       </c>
       <c r="B764" t="s" s="0">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E764" t="s" s="1">
         <v>18</v>
@@ -8708,7 +8891,7 @@
         <v>19</v>
       </c>
       <c r="B765" t="s" s="0">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="766">
@@ -8736,13 +8919,13 @@
         <v>1.0</v>
       </c>
       <c r="B767" t="s" s="3">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C767" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D767" t="s" s="3">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="E767" t="s" s="3">
         <v>28</v>
@@ -8756,7 +8939,7 @@
         <v>30</v>
       </c>
       <c r="B768" t="s" s="0">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="771">
@@ -8764,13 +8947,13 @@
         <v>2</v>
       </c>
       <c r="B771" t="s" s="0">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C771" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D771" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="772">
@@ -8792,7 +8975,7 @@
         <v>16</v>
       </c>
       <c r="B773" t="s" s="0">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E773" t="s" s="1">
         <v>18</v>
@@ -8803,7 +8986,7 @@
         <v>19</v>
       </c>
       <c r="B774" t="s" s="0">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="775">
@@ -8831,13 +9014,13 @@
         <v>1.0</v>
       </c>
       <c r="B776" t="s" s="3">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C776" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D776" t="s" s="3">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="E776" t="s" s="3">
         <v>28</v>
@@ -8851,7 +9034,7 @@
         <v>30</v>
       </c>
       <c r="B777" t="s" s="0">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="780">
@@ -8859,13 +9042,13 @@
         <v>2</v>
       </c>
       <c r="B780" t="s" s="0">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C780" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D780" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="781">
@@ -8873,7 +9056,7 @@
         <v>12</v>
       </c>
       <c r="B781" t="s" s="0">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C781" t="s" s="1">
         <v>14</v>
@@ -8887,7 +9070,7 @@
         <v>16</v>
       </c>
       <c r="B782" t="s" s="0">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="E782" t="s" s="1">
         <v>18</v>
@@ -8898,7 +9081,7 @@
         <v>19</v>
       </c>
       <c r="B783" t="s" s="0">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="784">
@@ -8926,13 +9109,13 @@
         <v>1.0</v>
       </c>
       <c r="B785" t="s" s="3">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C785" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D785" t="s" s="3">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="E785" t="s" s="3">
         <v>28</v>
@@ -8946,7 +9129,7 @@
         <v>30</v>
       </c>
       <c r="B786" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="789">
@@ -8954,13 +9137,13 @@
         <v>2</v>
       </c>
       <c r="B789" t="s" s="0">
-        <v>87</v>
+        <v>179</v>
       </c>
       <c r="C789" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D789" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="790">
@@ -8968,7 +9151,7 @@
         <v>12</v>
       </c>
       <c r="B790" t="s" s="0">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C790" t="s" s="1">
         <v>14</v>
@@ -8982,7 +9165,7 @@
         <v>16</v>
       </c>
       <c r="B791" t="s" s="0">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="E791" t="s" s="1">
         <v>18</v>
@@ -8993,7 +9176,7 @@
         <v>19</v>
       </c>
       <c r="B792" t="s" s="0">
-        <v>88</v>
+        <v>180</v>
       </c>
     </row>
     <row r="793">
@@ -9021,7 +9204,7 @@
         <v>1.0</v>
       </c>
       <c r="B794" t="s" s="3">
-        <v>91</v>
+        <v>181</v>
       </c>
       <c r="C794" t="s" s="3">
         <v>28</v>
@@ -9049,13 +9232,13 @@
         <v>2</v>
       </c>
       <c r="B798" t="s" s="0">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="C798" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D798" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="799">
@@ -9063,7 +9246,7 @@
         <v>12</v>
       </c>
       <c r="B799" t="s" s="0">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C799" t="s" s="1">
         <v>14</v>
@@ -9077,7 +9260,7 @@
         <v>16</v>
       </c>
       <c r="B800" t="s" s="0">
-        <v>17</v>
+        <v>182</v>
       </c>
       <c r="E800" t="s" s="1">
         <v>18</v>
@@ -9088,7 +9271,7 @@
         <v>19</v>
       </c>
       <c r="B801" t="s" s="0">
-        <v>93</v>
+        <v>180</v>
       </c>
     </row>
     <row r="802">
@@ -9116,7 +9299,7 @@
         <v>1.0</v>
       </c>
       <c r="B803" t="s" s="3">
-        <v>94</v>
+        <v>183</v>
       </c>
       <c r="C803" t="s" s="3">
         <v>28</v>
@@ -9144,13 +9327,13 @@
         <v>2</v>
       </c>
       <c r="B807" t="s" s="0">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="C807" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D807" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="808">
@@ -9158,7 +9341,7 @@
         <v>12</v>
       </c>
       <c r="B808" t="s" s="0">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C808" t="s" s="1">
         <v>14</v>
@@ -9172,7 +9355,7 @@
         <v>16</v>
       </c>
       <c r="B809" t="s" s="0">
-        <v>95</v>
+        <v>184</v>
       </c>
       <c r="E809" t="s" s="1">
         <v>18</v>
@@ -9183,7 +9366,7 @@
         <v>19</v>
       </c>
       <c r="B810" t="s" s="0">
-        <v>93</v>
+        <v>180</v>
       </c>
     </row>
     <row r="811">
@@ -9211,7 +9394,7 @@
         <v>1.0</v>
       </c>
       <c r="B812" t="s" s="3">
-        <v>96</v>
+        <v>185</v>
       </c>
       <c r="C812" t="s" s="3">
         <v>28</v>
@@ -9239,13 +9422,13 @@
         <v>2</v>
       </c>
       <c r="B816" t="s" s="0">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="C816" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D816" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="817">
@@ -9253,7 +9436,7 @@
         <v>12</v>
       </c>
       <c r="B817" t="s" s="0">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C817" t="s" s="1">
         <v>14</v>
@@ -9267,7 +9450,7 @@
         <v>16</v>
       </c>
       <c r="B818" t="s" s="0">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="E818" t="s" s="1">
         <v>18</v>
@@ -9278,7 +9461,7 @@
         <v>19</v>
       </c>
       <c r="B819" t="s" s="0">
-        <v>93</v>
+        <v>180</v>
       </c>
     </row>
     <row r="820">
@@ -9306,13 +9489,13 @@
         <v>1.0</v>
       </c>
       <c r="B821" t="s" s="3">
-        <v>98</v>
+        <v>181</v>
       </c>
       <c r="C821" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D821" t="s" s="3">
-        <v>48</v>
+        <v>186</v>
       </c>
       <c r="E821" t="s" s="3">
         <v>28</v>
@@ -9326,7 +9509,7 @@
         <v>30</v>
       </c>
       <c r="B822" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="825">
@@ -9334,13 +9517,13 @@
         <v>2</v>
       </c>
       <c r="B825" t="s" s="0">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="C825" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D825" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="826">
@@ -9348,7 +9531,7 @@
         <v>12</v>
       </c>
       <c r="B826" t="s" s="0">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C826" t="s" s="1">
         <v>14</v>
@@ -9362,7 +9545,7 @@
         <v>16</v>
       </c>
       <c r="B827" t="s" s="0">
-        <v>42</v>
+        <v>187</v>
       </c>
       <c r="E827" t="s" s="1">
         <v>18</v>
@@ -9373,7 +9556,7 @@
         <v>19</v>
       </c>
       <c r="B828" t="s" s="0">
-        <v>93</v>
+        <v>180</v>
       </c>
     </row>
     <row r="829">
@@ -9401,13 +9584,13 @@
         <v>1.0</v>
       </c>
       <c r="B830" t="s" s="3">
-        <v>94</v>
+        <v>181</v>
       </c>
       <c r="C830" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D830" t="s" s="3">
-        <v>99</v>
+        <v>188</v>
       </c>
       <c r="E830" t="s" s="3">
         <v>28</v>
@@ -9429,13 +9612,13 @@
         <v>2</v>
       </c>
       <c r="B834" t="s" s="0">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="C834" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D834" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="835">
@@ -9443,7 +9626,7 @@
         <v>12</v>
       </c>
       <c r="B835" t="s" s="0">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="C835" t="s" s="1">
         <v>14</v>
@@ -9457,7 +9640,7 @@
         <v>16</v>
       </c>
       <c r="B836" t="s" s="0">
-        <v>17</v>
+        <v>189</v>
       </c>
       <c r="E836" t="s" s="1">
         <v>18</v>
@@ -9468,7 +9651,7 @@
         <v>19</v>
       </c>
       <c r="B837" t="s" s="0">
-        <v>101</v>
+        <v>180</v>
       </c>
     </row>
     <row r="838">
@@ -9496,13 +9679,13 @@
         <v>1.0</v>
       </c>
       <c r="B839" t="s" s="3">
-        <v>102</v>
+        <v>181</v>
       </c>
       <c r="C839" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D839" t="s" s="3">
-        <v>48</v>
+        <v>190</v>
       </c>
       <c r="E839" t="s" s="3">
         <v>28</v>
@@ -9516,7 +9699,7 @@
         <v>30</v>
       </c>
       <c r="B840" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="843">
@@ -9524,13 +9707,13 @@
         <v>2</v>
       </c>
       <c r="B843" t="s" s="0">
-        <v>100</v>
+        <v>191</v>
       </c>
       <c r="C843" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D843" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="844">
@@ -9538,7 +9721,7 @@
         <v>12</v>
       </c>
       <c r="B844" t="s" s="0">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C844" t="s" s="1">
         <v>14</v>
@@ -9552,7 +9735,7 @@
         <v>16</v>
       </c>
       <c r="B845" t="s" s="0">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="E845" t="s" s="1">
         <v>18</v>
@@ -9563,7 +9746,7 @@
         <v>19</v>
       </c>
       <c r="B846" t="s" s="0">
-        <v>101</v>
+        <v>192</v>
       </c>
     </row>
     <row r="847">
@@ -9591,7 +9774,7 @@
         <v>1.0</v>
       </c>
       <c r="B848" t="s" s="3">
-        <v>104</v>
+        <v>193</v>
       </c>
       <c r="C848" t="s" s="3">
         <v>28</v>
@@ -9619,13 +9802,13 @@
         <v>2</v>
       </c>
       <c r="B852" t="s" s="0">
-        <v>100</v>
+        <v>191</v>
       </c>
       <c r="C852" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D852" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="853">
@@ -9633,7 +9816,7 @@
         <v>12</v>
       </c>
       <c r="B853" t="s" s="0">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C853" t="s" s="1">
         <v>14</v>
@@ -9647,7 +9830,7 @@
         <v>16</v>
       </c>
       <c r="B854" t="s" s="0">
-        <v>42</v>
+        <v>194</v>
       </c>
       <c r="E854" t="s" s="1">
         <v>18</v>
@@ -9658,7 +9841,7 @@
         <v>19</v>
       </c>
       <c r="B855" t="s" s="0">
-        <v>101</v>
+        <v>192</v>
       </c>
     </row>
     <row r="856">
@@ -9686,13 +9869,13 @@
         <v>1.0</v>
       </c>
       <c r="B857" t="s" s="3">
-        <v>102</v>
+        <v>193</v>
       </c>
       <c r="C857" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D857" t="s" s="3">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="E857" t="s" s="3">
         <v>28</v>
@@ -9714,13 +9897,13 @@
         <v>2</v>
       </c>
       <c r="B861" t="s" s="0">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="C861" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D861" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="862">
@@ -9753,7 +9936,7 @@
         <v>19</v>
       </c>
       <c r="B864" t="s" s="0">
-        <v>107</v>
+        <v>197</v>
       </c>
     </row>
     <row r="865">
@@ -9781,13 +9964,13 @@
         <v>1.0</v>
       </c>
       <c r="B866" t="s" s="3">
-        <v>108</v>
+        <v>198</v>
       </c>
       <c r="C866" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D866" t="s" s="3">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="E866" t="s" s="3">
         <v>28</v>
@@ -9801,7 +9984,7 @@
         <v>30</v>
       </c>
       <c r="B867" t="s" s="0">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="870">
@@ -9809,13 +9992,13 @@
         <v>2</v>
       </c>
       <c r="B870" t="s" s="0">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="C870" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D870" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="871">
@@ -9837,7 +10020,7 @@
         <v>16</v>
       </c>
       <c r="B872" t="s" s="0">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="E872" t="s" s="1">
         <v>18</v>
@@ -9848,7 +10031,7 @@
         <v>19</v>
       </c>
       <c r="B873" t="s" s="0">
-        <v>107</v>
+        <v>197</v>
       </c>
     </row>
     <row r="874">
@@ -9876,13 +10059,13 @@
         <v>1.0</v>
       </c>
       <c r="B875" t="s" s="3">
-        <v>111</v>
+        <v>201</v>
       </c>
       <c r="C875" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D875" t="s" s="3">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="E875" t="s" s="3">
         <v>28</v>
@@ -9896,7 +10079,7 @@
         <v>30</v>
       </c>
       <c r="B876" t="s" s="0">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="879">
@@ -9904,13 +10087,13 @@
         <v>2</v>
       </c>
       <c r="B879" t="s" s="0">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="C879" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D879" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="880">
@@ -9932,7 +10115,7 @@
         <v>16</v>
       </c>
       <c r="B881" t="s" s="0">
-        <v>112</v>
+        <v>202</v>
       </c>
       <c r="E881" t="s" s="1">
         <v>18</v>
@@ -9943,7 +10126,7 @@
         <v>19</v>
       </c>
       <c r="B882" t="s" s="0">
-        <v>107</v>
+        <v>197</v>
       </c>
     </row>
     <row r="883">
@@ -9971,13 +10154,13 @@
         <v>1.0</v>
       </c>
       <c r="B884" t="s" s="3">
-        <v>113</v>
+        <v>203</v>
       </c>
       <c r="C884" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D884" t="s" s="3">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="E884" t="s" s="3">
         <v>28</v>
@@ -9991,7 +10174,7 @@
         <v>30</v>
       </c>
       <c r="B885" t="s" s="0">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="888">
@@ -9999,13 +10182,13 @@
         <v>2</v>
       </c>
       <c r="B888" t="s" s="0">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="C888" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D888" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="889">
@@ -10027,7 +10210,7 @@
         <v>16</v>
       </c>
       <c r="B890" t="s" s="0">
-        <v>114</v>
+        <v>204</v>
       </c>
       <c r="E890" t="s" s="1">
         <v>18</v>
@@ -10038,7 +10221,7 @@
         <v>19</v>
       </c>
       <c r="B891" t="s" s="0">
-        <v>107</v>
+        <v>197</v>
       </c>
     </row>
     <row r="892">
@@ -10066,13 +10249,13 @@
         <v>1.0</v>
       </c>
       <c r="B893" t="s" s="3">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="C893" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D893" t="s" s="3">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="E893" t="s" s="3">
         <v>28</v>
@@ -10086,7 +10269,7 @@
         <v>30</v>
       </c>
       <c r="B894" t="s" s="0">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="897">
@@ -10094,13 +10277,13 @@
         <v>2</v>
       </c>
       <c r="B897" t="s" s="0">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="C897" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D897" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="898">
@@ -10122,7 +10305,7 @@
         <v>16</v>
       </c>
       <c r="B899" t="s" s="0">
-        <v>42</v>
+        <v>206</v>
       </c>
       <c r="E899" t="s" s="1">
         <v>18</v>
@@ -10133,7 +10316,7 @@
         <v>19</v>
       </c>
       <c r="B900" t="s" s="0">
-        <v>107</v>
+        <v>197</v>
       </c>
     </row>
     <row r="901">
@@ -10161,13 +10344,13 @@
         <v>1.0</v>
       </c>
       <c r="B902" t="s" s="3">
-        <v>108</v>
+        <v>207</v>
       </c>
       <c r="C902" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D902" t="s" s="3">
-        <v>116</v>
+        <v>199</v>
       </c>
       <c r="E902" t="s" s="3">
         <v>28</v>
@@ -10181,7 +10364,7 @@
         <v>30</v>
       </c>
       <c r="B903" t="s" s="0">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="906">
@@ -10189,13 +10372,13 @@
         <v>2</v>
       </c>
       <c r="B906" t="s" s="0">
-        <v>117</v>
+        <v>196</v>
       </c>
       <c r="C906" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D906" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="907">
@@ -10203,7 +10386,7 @@
         <v>12</v>
       </c>
       <c r="B907" t="s" s="0">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="C907" t="s" s="1">
         <v>14</v>
@@ -10217,7 +10400,7 @@
         <v>16</v>
       </c>
       <c r="B908" t="s" s="0">
-        <v>17</v>
+        <v>208</v>
       </c>
       <c r="E908" t="s" s="1">
         <v>18</v>
@@ -10228,7 +10411,7 @@
         <v>19</v>
       </c>
       <c r="B909" t="s" s="0">
-        <v>107</v>
+        <v>197</v>
       </c>
     </row>
     <row r="910">
@@ -10256,13 +10439,13 @@
         <v>1.0</v>
       </c>
       <c r="B911" t="s" s="3">
-        <v>118</v>
+        <v>209</v>
       </c>
       <c r="C911" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D911" t="s" s="3">
-        <v>48</v>
+        <v>199</v>
       </c>
       <c r="E911" t="s" s="3">
         <v>28</v>
@@ -10276,7 +10459,7 @@
         <v>30</v>
       </c>
       <c r="B912" t="s" s="0">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="915">
@@ -10284,13 +10467,13 @@
         <v>2</v>
       </c>
       <c r="B915" t="s" s="0">
-        <v>117</v>
+        <v>196</v>
       </c>
       <c r="C915" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D915" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="916">
@@ -10298,7 +10481,7 @@
         <v>12</v>
       </c>
       <c r="B916" t="s" s="0">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="C916" t="s" s="1">
         <v>14</v>
@@ -10312,7 +10495,7 @@
         <v>16</v>
       </c>
       <c r="B917" t="s" s="0">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="E917" t="s" s="1">
         <v>18</v>
@@ -10323,7 +10506,7 @@
         <v>19</v>
       </c>
       <c r="B918" t="s" s="0">
-        <v>107</v>
+        <v>197</v>
       </c>
     </row>
     <row r="919">
@@ -10351,13 +10534,13 @@
         <v>1.0</v>
       </c>
       <c r="B920" t="s" s="3">
-        <v>120</v>
+        <v>198</v>
       </c>
       <c r="C920" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D920" t="s" s="3">
-        <v>48</v>
+        <v>210</v>
       </c>
       <c r="E920" t="s" s="3">
         <v>28</v>
@@ -10371,7 +10554,7 @@
         <v>30</v>
       </c>
       <c r="B921" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="924">
@@ -10379,13 +10562,13 @@
         <v>2</v>
       </c>
       <c r="B924" t="s" s="0">
-        <v>117</v>
+        <v>211</v>
       </c>
       <c r="C924" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D924" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="925">
@@ -10393,7 +10576,7 @@
         <v>12</v>
       </c>
       <c r="B925" t="s" s="0">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C925" t="s" s="1">
         <v>14</v>
@@ -10407,7 +10590,7 @@
         <v>16</v>
       </c>
       <c r="B926" t="s" s="0">
-        <v>121</v>
+        <v>17</v>
       </c>
       <c r="E926" t="s" s="1">
         <v>18</v>
@@ -10418,7 +10601,7 @@
         <v>19</v>
       </c>
       <c r="B927" t="s" s="0">
-        <v>107</v>
+        <v>212</v>
       </c>
     </row>
     <row r="928">
@@ -10446,13 +10629,13 @@
         <v>1.0</v>
       </c>
       <c r="B929" t="s" s="3">
-        <v>122</v>
+        <v>213</v>
       </c>
       <c r="C929" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D929" t="s" s="3">
-        <v>48</v>
+        <v>214</v>
       </c>
       <c r="E929" t="s" s="3">
         <v>28</v>
@@ -10466,7 +10649,7 @@
         <v>30</v>
       </c>
       <c r="B930" t="s" s="0">
-        <v>49</v>
+        <v>94</v>
       </c>
     </row>
     <row r="933">
@@ -10474,13 +10657,13 @@
         <v>2</v>
       </c>
       <c r="B933" t="s" s="0">
-        <v>117</v>
+        <v>211</v>
       </c>
       <c r="C933" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D933" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="934">
@@ -10488,7 +10671,7 @@
         <v>12</v>
       </c>
       <c r="B934" t="s" s="0">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C934" t="s" s="1">
         <v>14</v>
@@ -10502,7 +10685,7 @@
         <v>16</v>
       </c>
       <c r="B935" t="s" s="0">
-        <v>42</v>
+        <v>215</v>
       </c>
       <c r="E935" t="s" s="1">
         <v>18</v>
@@ -10513,7 +10696,7 @@
         <v>19</v>
       </c>
       <c r="B936" t="s" s="0">
-        <v>107</v>
+        <v>212</v>
       </c>
     </row>
     <row r="937">
@@ -10541,13 +10724,13 @@
         <v>1.0</v>
       </c>
       <c r="B938" t="s" s="3">
-        <v>118</v>
+        <v>216</v>
       </c>
       <c r="C938" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D938" t="s" s="3">
-        <v>123</v>
+        <v>214</v>
       </c>
       <c r="E938" t="s" s="3">
         <v>28</v>
@@ -10561,7 +10744,7 @@
         <v>30</v>
       </c>
       <c r="B939" t="s" s="0">
-        <v>44</v>
+        <v>94</v>
       </c>
     </row>
     <row r="942">
@@ -10569,13 +10752,13 @@
         <v>2</v>
       </c>
       <c r="B942" t="s" s="0">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="C942" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D942" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="943">
@@ -10583,7 +10766,7 @@
         <v>12</v>
       </c>
       <c r="B943" t="s" s="0">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C943" t="s" s="1">
         <v>14</v>
@@ -10597,7 +10780,7 @@
         <v>16</v>
       </c>
       <c r="B944" t="s" s="0">
-        <v>17</v>
+        <v>217</v>
       </c>
       <c r="E944" t="s" s="1">
         <v>18</v>
@@ -10608,7 +10791,7 @@
         <v>19</v>
       </c>
       <c r="B945" t="s" s="0">
-        <v>125</v>
+        <v>212</v>
       </c>
     </row>
     <row r="946">
@@ -10636,13 +10819,13 @@
         <v>1.0</v>
       </c>
       <c r="B947" t="s" s="3">
-        <v>126</v>
+        <v>218</v>
       </c>
       <c r="C947" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D947" t="s" s="3">
-        <v>48</v>
+        <v>214</v>
       </c>
       <c r="E947" t="s" s="3">
         <v>28</v>
@@ -10656,7 +10839,7 @@
         <v>30</v>
       </c>
       <c r="B948" t="s" s="0">
-        <v>31</v>
+        <v>94</v>
       </c>
     </row>
     <row r="951">
@@ -10664,13 +10847,13 @@
         <v>2</v>
       </c>
       <c r="B951" t="s" s="0">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="C951" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D951" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="952">
@@ -10678,7 +10861,7 @@
         <v>12</v>
       </c>
       <c r="B952" t="s" s="0">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C952" t="s" s="1">
         <v>14</v>
@@ -10692,7 +10875,7 @@
         <v>16</v>
       </c>
       <c r="B953" t="s" s="0">
-        <v>127</v>
+        <v>219</v>
       </c>
       <c r="E953" t="s" s="1">
         <v>18</v>
@@ -10703,7 +10886,7 @@
         <v>19</v>
       </c>
       <c r="B954" t="s" s="0">
-        <v>125</v>
+        <v>212</v>
       </c>
     </row>
     <row r="955">
@@ -10731,13 +10914,13 @@
         <v>1.0</v>
       </c>
       <c r="B956" t="s" s="3">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="C956" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D956" t="s" s="3">
-        <v>48</v>
+        <v>214</v>
       </c>
       <c r="E956" t="s" s="3">
         <v>28</v>
@@ -10751,7 +10934,7 @@
         <v>30</v>
       </c>
       <c r="B957" t="s" s="0">
-        <v>31</v>
+        <v>94</v>
       </c>
     </row>
     <row r="960">
@@ -10759,13 +10942,13 @@
         <v>2</v>
       </c>
       <c r="B960" t="s" s="0">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="C960" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D960" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="961">
@@ -10773,7 +10956,7 @@
         <v>12</v>
       </c>
       <c r="B961" t="s" s="0">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C961" t="s" s="1">
         <v>14</v>
@@ -10787,7 +10970,7 @@
         <v>16</v>
       </c>
       <c r="B962" t="s" s="0">
-        <v>129</v>
+        <v>221</v>
       </c>
       <c r="E962" t="s" s="1">
         <v>18</v>
@@ -10798,7 +10981,7 @@
         <v>19</v>
       </c>
       <c r="B963" t="s" s="0">
-        <v>125</v>
+        <v>212</v>
       </c>
     </row>
     <row r="964">
@@ -10826,13 +11009,13 @@
         <v>1.0</v>
       </c>
       <c r="B965" t="s" s="3">
-        <v>130</v>
+        <v>222</v>
       </c>
       <c r="C965" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D965" t="s" s="3">
-        <v>48</v>
+        <v>214</v>
       </c>
       <c r="E965" t="s" s="3">
         <v>28</v>
@@ -10846,7 +11029,7 @@
         <v>30</v>
       </c>
       <c r="B966" t="s" s="0">
-        <v>31</v>
+        <v>94</v>
       </c>
     </row>
     <row r="969">
@@ -10854,13 +11037,13 @@
         <v>2</v>
       </c>
       <c r="B969" t="s" s="0">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="C969" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D969" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="970">
@@ -10868,7 +11051,7 @@
         <v>12</v>
       </c>
       <c r="B970" t="s" s="0">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C970" t="s" s="1">
         <v>14</v>
@@ -10882,7 +11065,7 @@
         <v>16</v>
       </c>
       <c r="B971" t="s" s="0">
-        <v>131</v>
+        <v>223</v>
       </c>
       <c r="E971" t="s" s="1">
         <v>18</v>
@@ -10893,7 +11076,7 @@
         <v>19</v>
       </c>
       <c r="B972" t="s" s="0">
-        <v>125</v>
+        <v>212</v>
       </c>
     </row>
     <row r="973">
@@ -10921,13 +11104,13 @@
         <v>1.0</v>
       </c>
       <c r="B974" t="s" s="3">
-        <v>132</v>
+        <v>224</v>
       </c>
       <c r="C974" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D974" t="s" s="3">
-        <v>48</v>
+        <v>214</v>
       </c>
       <c r="E974" t="s" s="3">
         <v>28</v>
@@ -10941,7 +11124,7 @@
         <v>30</v>
       </c>
       <c r="B975" t="s" s="0">
-        <v>31</v>
+        <v>94</v>
       </c>
     </row>
     <row r="978">
@@ -10949,13 +11132,13 @@
         <v>2</v>
       </c>
       <c r="B978" t="s" s="0">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="C978" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D978" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="979">
@@ -10963,7 +11146,7 @@
         <v>12</v>
       </c>
       <c r="B979" t="s" s="0">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="C979" t="s" s="1">
         <v>14</v>
@@ -10977,7 +11160,7 @@
         <v>16</v>
       </c>
       <c r="B980" t="s" s="0">
-        <v>133</v>
+        <v>225</v>
       </c>
       <c r="E980" t="s" s="1">
         <v>18</v>
@@ -10988,7 +11171,7 @@
         <v>19</v>
       </c>
       <c r="B981" t="s" s="0">
-        <v>125</v>
+        <v>212</v>
       </c>
     </row>
     <row r="982">
@@ -11016,13 +11199,13 @@
         <v>1.0</v>
       </c>
       <c r="B983" t="s" s="3">
-        <v>134</v>
+        <v>226</v>
       </c>
       <c r="C983" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D983" t="s" s="3">
-        <v>48</v>
+        <v>214</v>
       </c>
       <c r="E983" t="s" s="3">
         <v>28</v>
@@ -11036,7 +11219,7 @@
         <v>30</v>
       </c>
       <c r="B984" t="s" s="0">
-        <v>31</v>
+        <v>94</v>
       </c>
     </row>
     <row r="987">
@@ -11044,13 +11227,13 @@
         <v>2</v>
       </c>
       <c r="B987" t="s" s="0">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="C987" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D987" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="988">
@@ -11058,7 +11241,7 @@
         <v>12</v>
       </c>
       <c r="B988" t="s" s="0">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="C988" t="s" s="1">
         <v>14</v>
@@ -11083,7 +11266,7 @@
         <v>19</v>
       </c>
       <c r="B990" t="s" s="0">
-        <v>125</v>
+        <v>212</v>
       </c>
     </row>
     <row r="991">
@@ -11111,13 +11294,13 @@
         <v>1.0</v>
       </c>
       <c r="B992" t="s" s="3">
-        <v>126</v>
+        <v>213</v>
       </c>
       <c r="C992" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D992" t="s" s="3">
-        <v>135</v>
+        <v>227</v>
       </c>
       <c r="E992" t="s" s="3">
         <v>28</v>
@@ -11139,13 +11322,13 @@
         <v>2</v>
       </c>
       <c r="B996" t="s" s="0">
-        <v>136</v>
+        <v>228</v>
       </c>
       <c r="C996" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D996" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="997">
@@ -11178,7 +11361,7 @@
         <v>19</v>
       </c>
       <c r="B999" t="s" s="0">
-        <v>137</v>
+        <v>229</v>
       </c>
     </row>
     <row r="1000">
@@ -11206,7 +11389,7 @@
         <v>1.0</v>
       </c>
       <c r="B1001" t="s" s="3">
-        <v>138</v>
+        <v>230</v>
       </c>
       <c r="C1001" t="s" s="3">
         <v>28</v>
@@ -11234,13 +11417,13 @@
         <v>2</v>
       </c>
       <c r="B1005" t="s" s="0">
-        <v>136</v>
+        <v>228</v>
       </c>
       <c r="C1005" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D1005" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1006">
@@ -11262,7 +11445,7 @@
         <v>16</v>
       </c>
       <c r="B1007" t="s" s="0">
-        <v>139</v>
+        <v>231</v>
       </c>
       <c r="E1007" t="s" s="1">
         <v>18</v>
@@ -11273,7 +11456,7 @@
         <v>19</v>
       </c>
       <c r="B1008" t="s" s="0">
-        <v>137</v>
+        <v>229</v>
       </c>
     </row>
     <row r="1009">
@@ -11301,13 +11484,13 @@
         <v>1.0</v>
       </c>
       <c r="B1010" t="s" s="3">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="C1010" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D1010" t="s" s="3">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="E1010" t="s" s="3">
         <v>28</v>
@@ -11321,7 +11504,7 @@
         <v>30</v>
       </c>
       <c r="B1011" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1014">
@@ -11329,13 +11512,13 @@
         <v>2</v>
       </c>
       <c r="B1014" t="s" s="0">
-        <v>136</v>
+        <v>228</v>
       </c>
       <c r="C1014" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D1014" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1015">
@@ -11357,7 +11540,7 @@
         <v>16</v>
       </c>
       <c r="B1016" t="s" s="0">
-        <v>141</v>
+        <v>233</v>
       </c>
       <c r="E1016" t="s" s="1">
         <v>18</v>
@@ -11368,7 +11551,7 @@
         <v>19</v>
       </c>
       <c r="B1017" t="s" s="0">
-        <v>137</v>
+        <v>229</v>
       </c>
     </row>
     <row r="1018">
@@ -11396,13 +11579,13 @@
         <v>1.0</v>
       </c>
       <c r="B1019" t="s" s="3">
-        <v>142</v>
+        <v>230</v>
       </c>
       <c r="C1019" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D1019" t="s" s="3">
-        <v>48</v>
+        <v>234</v>
       </c>
       <c r="E1019" t="s" s="3">
         <v>28</v>
@@ -11416,7 +11599,7 @@
         <v>30</v>
       </c>
       <c r="B1020" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1023">
@@ -11424,13 +11607,13 @@
         <v>2</v>
       </c>
       <c r="B1023" t="s" s="0">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="C1023" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D1023" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1024">
@@ -11438,7 +11621,7 @@
         <v>12</v>
       </c>
       <c r="B1024" t="s" s="0">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C1024" t="s" s="1">
         <v>14</v>
@@ -11452,7 +11635,7 @@
         <v>16</v>
       </c>
       <c r="B1025" t="s" s="0">
-        <v>143</v>
+        <v>17</v>
       </c>
       <c r="E1025" t="s" s="1">
         <v>18</v>
@@ -11463,7 +11646,7 @@
         <v>19</v>
       </c>
       <c r="B1026" t="s" s="0">
-        <v>137</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1027">
@@ -11491,7 +11674,7 @@
         <v>1.0</v>
       </c>
       <c r="B1028" t="s" s="3">
-        <v>144</v>
+        <v>235</v>
       </c>
       <c r="C1028" t="s" s="3">
         <v>28</v>
@@ -11511,7 +11694,7 @@
         <v>30</v>
       </c>
       <c r="B1029" t="s" s="0">
-        <v>49</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1032">
@@ -11519,13 +11702,13 @@
         <v>2</v>
       </c>
       <c r="B1032" t="s" s="0">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="C1032" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D1032" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1033">
@@ -11533,7 +11716,7 @@
         <v>12</v>
       </c>
       <c r="B1033" t="s" s="0">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C1033" t="s" s="1">
         <v>14</v>
@@ -11547,7 +11730,7 @@
         <v>16</v>
       </c>
       <c r="B1034" t="s" s="0">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="E1034" t="s" s="1">
         <v>18</v>
@@ -11558,7 +11741,7 @@
         <v>19</v>
       </c>
       <c r="B1035" t="s" s="0">
-        <v>137</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1036">
@@ -11586,7 +11769,7 @@
         <v>1.0</v>
       </c>
       <c r="B1037" t="s" s="3">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="C1037" t="s" s="3">
         <v>28</v>
@@ -11606,7 +11789,7 @@
         <v>30</v>
       </c>
       <c r="B1038" t="s" s="0">
-        <v>49</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1041">
@@ -11614,13 +11797,13 @@
         <v>2</v>
       </c>
       <c r="B1041" t="s" s="0">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="C1041" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D1041" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1042">
@@ -11628,7 +11811,7 @@
         <v>12</v>
       </c>
       <c r="B1042" t="s" s="0">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="C1042" t="s" s="1">
         <v>14</v>
@@ -11642,7 +11825,7 @@
         <v>16</v>
       </c>
       <c r="B1043" t="s" s="0">
-        <v>147</v>
+        <v>42</v>
       </c>
       <c r="E1043" t="s" s="1">
         <v>18</v>
@@ -11653,7 +11836,7 @@
         <v>19</v>
       </c>
       <c r="B1044" t="s" s="0">
-        <v>137</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1045">
@@ -11681,13 +11864,13 @@
         <v>1.0</v>
       </c>
       <c r="B1046" t="s" s="3">
-        <v>148</v>
+        <v>235</v>
       </c>
       <c r="C1046" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D1046" t="s" s="3">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="E1046" t="s" s="3">
         <v>28</v>
@@ -11701,7 +11884,7 @@
         <v>30</v>
       </c>
       <c r="B1047" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1050">
@@ -11709,13 +11892,13 @@
         <v>2</v>
       </c>
       <c r="B1050" t="s" s="0">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="C1050" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D1050" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1051">
@@ -11723,7 +11906,7 @@
         <v>12</v>
       </c>
       <c r="B1051" t="s" s="0">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="C1051" t="s" s="1">
         <v>14</v>
@@ -11737,7 +11920,7 @@
         <v>16</v>
       </c>
       <c r="B1052" t="s" s="0">
-        <v>149</v>
+        <v>54</v>
       </c>
       <c r="E1052" t="s" s="1">
         <v>18</v>
@@ -11748,7 +11931,7 @@
         <v>19</v>
       </c>
       <c r="B1053" t="s" s="0">
-        <v>137</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1054">
@@ -11776,13 +11959,13 @@
         <v>1.0</v>
       </c>
       <c r="B1055" t="s" s="3">
-        <v>150</v>
+        <v>235</v>
       </c>
       <c r="C1055" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D1055" t="s" s="3">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="E1055" t="s" s="3">
         <v>28</v>
@@ -11796,7 +11979,7 @@
         <v>30</v>
       </c>
       <c r="B1056" t="s" s="0">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1059">
@@ -11804,13 +11987,13 @@
         <v>2</v>
       </c>
       <c r="B1059" t="s" s="0">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="C1059" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D1059" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1060">
@@ -11818,7 +12001,7 @@
         <v>12</v>
       </c>
       <c r="B1060" t="s" s="0">
-        <v>151</v>
+        <v>13</v>
       </c>
       <c r="C1060" t="s" s="1">
         <v>14</v>
@@ -11832,7 +12015,7 @@
         <v>16</v>
       </c>
       <c r="B1061" t="s" s="0">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="E1061" t="s" s="1">
         <v>18</v>
@@ -11843,7 +12026,7 @@
         <v>19</v>
       </c>
       <c r="B1062" t="s" s="0">
-        <v>137</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1063">
@@ -11871,7 +12054,7 @@
         <v>1.0</v>
       </c>
       <c r="B1064" t="s" s="3">
-        <v>153</v>
+        <v>101</v>
       </c>
       <c r="C1064" t="s" s="3">
         <v>28</v>
@@ -11899,13 +12082,13 @@
         <v>2</v>
       </c>
       <c r="B1068" t="s" s="0">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="C1068" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D1068" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1069">
@@ -11913,7 +12096,7 @@
         <v>12</v>
       </c>
       <c r="B1069" t="s" s="0">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="C1069" t="s" s="1">
         <v>14</v>
@@ -11927,7 +12110,7 @@
         <v>16</v>
       </c>
       <c r="B1070" t="s" s="0">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="E1070" t="s" s="1">
         <v>18</v>
@@ -11938,7 +12121,7 @@
         <v>19</v>
       </c>
       <c r="B1071" t="s" s="0">
-        <v>137</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1072">
@@ -11966,13 +12149,13 @@
         <v>1.0</v>
       </c>
       <c r="B1073" t="s" s="3">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="C1073" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D1073" t="s" s="3">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="E1073" t="s" s="3">
         <v>28</v>
@@ -11994,13 +12177,13 @@
         <v>2</v>
       </c>
       <c r="B1077" t="s" s="0">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="C1077" t="s" s="1">
         <v>10</v>
       </c>
       <c r="D1077" t="s" s="0">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1078">
@@ -12008,7 +12191,7 @@
         <v>12</v>
       </c>
       <c r="B1078" t="s" s="0">
-        <v>156</v>
+        <v>35</v>
       </c>
       <c r="C1078" t="s" s="1">
         <v>14</v>
@@ -12022,7 +12205,7 @@
         <v>16</v>
       </c>
       <c r="B1079" t="s" s="0">
-        <v>157</v>
+        <v>104</v>
       </c>
       <c r="E1079" t="s" s="1">
         <v>18</v>
@@ -12033,7 +12216,7 @@
         <v>19</v>
       </c>
       <c r="B1080" t="s" s="0">
-        <v>137</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1081">
@@ -12061,13 +12244,13 @@
         <v>1.0</v>
       </c>
       <c r="B1082" t="s" s="3">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="C1082" t="s" s="3">
         <v>28</v>
       </c>
       <c r="D1082" t="s" s="3">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E1082" t="s" s="3">
         <v>28</v>
@@ -12081,6 +12264,3426 @@
         <v>30</v>
       </c>
       <c r="B1083" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1086" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="C1086" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1086" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1087" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C1087" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1087" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1088" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E1088" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1089" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1090" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1090" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1090" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1090" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1090" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1091" t="s" s="3">
+        <v>108</v>
+      </c>
+      <c r="C1091" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1091" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1091" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1091" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1092" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1095" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="C1095" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1095" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1096" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C1096" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1096" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1097" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="E1097" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1098" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1099" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1099" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1099" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1099" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1099" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1100" t="s" s="3">
+        <v>110</v>
+      </c>
+      <c r="C1100" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1100" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1100" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1100" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1101" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1104" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="C1104" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1104" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1105" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C1105" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1105" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1106" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E1106" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1107" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1108" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1108" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1108" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1108" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1108" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1109" t="s" s="3">
+        <v>113</v>
+      </c>
+      <c r="C1109" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1109" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1109" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1109" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1110" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1113" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="C1113" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1113" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1114" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C1114" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1114" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1115" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="E1115" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1116" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1117" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1117" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1117" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1117" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1117" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1118" t="s" s="3">
+        <v>115</v>
+      </c>
+      <c r="C1118" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1118" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1118" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1118" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1119" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1122" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="C1122" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1122" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1123" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C1123" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1123" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1124" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="E1124" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1125" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1126" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1126" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1126" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1126" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1126" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1127" t="s" s="3">
+        <v>117</v>
+      </c>
+      <c r="C1127" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1127" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1127" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1127" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1128" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1131" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="C1131" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1131" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1132" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1132" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1132" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1133" t="s" s="0">
+        <v>236</v>
+      </c>
+      <c r="E1133" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1134" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1135" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1135" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1135" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1135" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1135" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1136" t="s" s="3">
+        <v>237</v>
+      </c>
+      <c r="C1136" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1136" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1136" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1136" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1137" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1140" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="C1140" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1140" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1141" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C1141" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1141" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1142" t="s" s="0">
+        <v>238</v>
+      </c>
+      <c r="E1142" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1143" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1144" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1144" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1144" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1144" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1144" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1145" t="s" s="3">
+        <v>239</v>
+      </c>
+      <c r="C1145" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1145" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1145" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1145" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1146" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1149" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="C1149" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1149" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1150" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="C1150" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1150" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1151" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="E1151" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1152" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1153" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1153" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1153" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1153" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1153" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1154" t="s" s="3">
+        <v>113</v>
+      </c>
+      <c r="C1154" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1154" t="s" s="3">
+        <v>118</v>
+      </c>
+      <c r="E1154" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1154" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1155" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1158" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="C1158" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1158" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1159" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C1159" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1159" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1160" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E1160" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1161" t="s" s="0">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1162" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1162" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1162" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1162" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1162" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1163" t="s" s="3">
+        <v>121</v>
+      </c>
+      <c r="C1163" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1163" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1163" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1163" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1164" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1167" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="C1167" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1167" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1168" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C1168" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1168" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1169" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="E1169" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1170" t="s" s="0">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1171" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1171" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1171" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1171" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1171" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1172" t="s" s="3">
+        <v>123</v>
+      </c>
+      <c r="C1172" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1172" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1172" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1172" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1173" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1176" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="C1176" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1176" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1177" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C1177" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1177" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1178" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="E1178" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1179" t="s" s="0">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1180" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1180" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1180" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1180" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1180" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1181" t="s" s="3">
+        <v>121</v>
+      </c>
+      <c r="C1181" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1181" t="s" s="3">
+        <v>124</v>
+      </c>
+      <c r="E1181" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1181" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1182" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1185" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="C1185" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1185" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1186" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C1186" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1186" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1187" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E1187" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1188" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1189" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1189" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1189" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1189" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1189" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1190" t="s" s="3">
+        <v>127</v>
+      </c>
+      <c r="C1190" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1190" t="s" s="3">
+        <v>128</v>
+      </c>
+      <c r="E1190" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1190" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1191" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1194" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="C1194" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1194" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1195" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C1195" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1195" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1196" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="E1196" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1197" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1198" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1198" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1198" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1198" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1198" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1199" t="s" s="3">
+        <v>130</v>
+      </c>
+      <c r="C1199" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1199" t="s" s="3">
+        <v>128</v>
+      </c>
+      <c r="E1199" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1199" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1200" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1203" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="C1203" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1203" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1204" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C1204" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1204" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1205" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="E1205" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1206" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1207" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1207" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1207" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1207" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1207" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1208" t="s" s="3">
+        <v>132</v>
+      </c>
+      <c r="C1208" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1208" t="s" s="3">
+        <v>128</v>
+      </c>
+      <c r="E1208" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1208" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1209" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1212" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="C1212" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1212" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1213" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1213" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1213" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1214" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="E1214" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1215" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1216" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1216" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1216" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1216" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1216" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1217" t="s" s="3">
+        <v>134</v>
+      </c>
+      <c r="C1217" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1217" t="s" s="3">
+        <v>128</v>
+      </c>
+      <c r="E1217" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1217" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1218" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1221" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="C1221" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1221" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1222" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C1222" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1222" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1223" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="E1223" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1224" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1225" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1225" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1225" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1225" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1225" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1226" t="s" s="3">
+        <v>127</v>
+      </c>
+      <c r="C1226" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1226" t="s" s="3">
+        <v>135</v>
+      </c>
+      <c r="E1226" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1226" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1227" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1230" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="C1230" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1230" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1231" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C1231" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1231" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1232" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E1232" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1233" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1234" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1234" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1234" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1234" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1234" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1235" t="s" s="3">
+        <v>137</v>
+      </c>
+      <c r="C1235" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1235" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1235" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1235" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1236" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1239" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="C1239" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1239" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1240" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C1240" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1240" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1241" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="E1241" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1242" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1243" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1243" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1243" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1243" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1244" t="s" s="3">
+        <v>139</v>
+      </c>
+      <c r="C1244" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1244" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1244" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1244" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1245" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1248" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="C1248" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1248" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1249" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C1249" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1249" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1250" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="E1250" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1251" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1252" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1252" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1252" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1252" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1253" t="s" s="3">
+        <v>141</v>
+      </c>
+      <c r="C1253" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1253" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1253" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1253" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1254" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1257" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="C1257" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1257" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1258" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1258" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1258" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1259" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="E1259" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1260" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1261" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1261" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1261" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1261" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1262" t="s" s="3">
+        <v>137</v>
+      </c>
+      <c r="C1262" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1262" t="s" s="3">
+        <v>142</v>
+      </c>
+      <c r="E1262" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1262" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1263" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1266" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="C1266" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1266" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1267" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C1267" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1267" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1268" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E1268" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1269" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1270" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1270" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1270" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1270" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1270" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1271" t="s" s="3">
+        <v>145</v>
+      </c>
+      <c r="C1271" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1271" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1271" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1271" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1272" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1275" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="C1275" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1275" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1276" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C1276" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1276" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1277" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="E1277" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1278" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1279" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1279" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1279" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1279" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1279" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1280" t="s" s="3">
+        <v>147</v>
+      </c>
+      <c r="C1280" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1280" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1280" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1280" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1281" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1284" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="C1284" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1284" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1285" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C1285" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1285" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1286" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="E1286" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1287" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1288" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1288" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1288" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1288" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1288" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1289" t="s" s="3">
+        <v>149</v>
+      </c>
+      <c r="C1289" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1289" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1289" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1289" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1290" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1293" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="C1293" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1293" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1294" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1294" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1294" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1295" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="E1295" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1296" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1297" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1297" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1297" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1297" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1297" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1298" t="s" s="3">
+        <v>151</v>
+      </c>
+      <c r="C1298" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1298" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1298" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1298" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1299" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1302" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="C1302" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1302" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1303" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C1303" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1303" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1304" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="E1304" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1305" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1306" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1306" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1306" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1306" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1306" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1307" t="s" s="3">
+        <v>153</v>
+      </c>
+      <c r="C1307" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1307" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1307" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1307" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1308" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1311" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="C1311" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1311" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1312" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="C1312" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1312" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1313" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="E1313" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1314" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1315" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1315" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1315" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1315" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1315" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1316" t="s" s="3">
+        <v>145</v>
+      </c>
+      <c r="C1316" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1316" t="s" s="3">
+        <v>154</v>
+      </c>
+      <c r="E1316" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1316" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1317" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1320" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="C1320" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1320" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1321" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C1321" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1321" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1322" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E1322" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1323" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1324" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1324" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1324" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1324" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1324" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1325" t="s" s="3">
+        <v>157</v>
+      </c>
+      <c r="C1325" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1325" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1325" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1325" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1326" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1329" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="C1329" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1329" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1330" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C1330" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1330" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1331" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="E1331" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1332" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1333" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1333" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1333" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1333" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1333" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1334" t="s" s="3">
+        <v>159</v>
+      </c>
+      <c r="C1334" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1334" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1334" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1334" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1335" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1338" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="C1338" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1338" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1339" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C1339" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1339" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1340" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="E1340" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1341" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1342" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1342" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1342" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1342" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1342" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1343" t="s" s="3">
+        <v>161</v>
+      </c>
+      <c r="C1343" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1343" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1343" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1343" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1344" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1347" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="C1347" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1347" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1348" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1348" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1348" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1349" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="E1349" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1350" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1351" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1351" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1351" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1351" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1351" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1352" t="s" s="3">
+        <v>163</v>
+      </c>
+      <c r="C1352" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1352" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1352" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1352" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1353" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1356" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="C1356" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1356" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1357" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C1357" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1357" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1358" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="E1358" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1359" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1360" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1360" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1360" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1360" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1360" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1361" t="s" s="3">
+        <v>165</v>
+      </c>
+      <c r="C1361" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1361" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1361" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1361" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1362" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1365" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="C1365" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1365" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1366" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="C1366" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1366" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1367" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="E1367" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1368" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1369" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1369" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1369" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1369" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1369" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1370" t="s" s="3">
+        <v>167</v>
+      </c>
+      <c r="C1370" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1370" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1370" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1370" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1371" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1374" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="C1374" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1374" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1375" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C1375" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1375" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1376" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="E1376" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1377" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1378" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1378" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1378" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1378" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1378" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1379" t="s" s="3">
+        <v>169</v>
+      </c>
+      <c r="C1379" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1379" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1379" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1379" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1380" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1383" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="C1383" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1383" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1384" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="C1384" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1384" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1385" t="s" s="0">
+        <v>171</v>
+      </c>
+      <c r="E1385" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1386" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1387" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1387" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1387" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1387" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1388" t="s" s="3">
+        <v>172</v>
+      </c>
+      <c r="C1388" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1388" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1388" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1388" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1389" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1392" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="C1392" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1392" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1393" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="C1393" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1393" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1394" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="E1394" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1395" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1396" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1396" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1396" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1396" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1397" t="s" s="3">
+        <v>157</v>
+      </c>
+      <c r="C1397" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1397" t="s" s="3">
+        <v>174</v>
+      </c>
+      <c r="E1397" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1397" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1398" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1401" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="C1401" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1401" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="B1402" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="C1402" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="E1402" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1403" t="s" s="0">
+        <v>176</v>
+      </c>
+      <c r="E1403" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1404" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C1405" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D1405" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E1405" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F1405" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B1406" t="s" s="3">
+        <v>157</v>
+      </c>
+      <c r="C1406" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1406" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="E1406" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1406" t="s" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1407" t="s" s="0">
         <v>44</v>
       </c>
     </row>
